--- a/Revalidacion Moose Scorpion Gecko/RA_Moose_Scorpion.xlsx
+++ b/Revalidacion Moose Scorpion Gecko/RA_Moose_Scorpion.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\4019461\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WorkPackages\PRD - 010\0E7E3A2646331FE182EF7606C92B36FC\in\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1B0DFFB-6522-44AF-B886-8F1AA429025D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F924BB51-F1F4-4822-8AF0-B100ABEC18A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="540" yWindow="480" windowWidth="18195" windowHeight="14145" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RA Form" sheetId="1" r:id="rId1"/>
@@ -327,7 +327,7 @@
     <definedName name="Vibracion_herramientas_ctrl">Listas_Controles!$CM$2:$CM$3</definedName>
     <definedName name="Vibracion_herramientas_epp">Listas_EPP!$CJ$2:$CJ$2</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -339,8 +339,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -453,7 +451,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2704" uniqueCount="1279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2563" uniqueCount="1242">
   <si>
     <t>PROCESO EVALUADO</t>
   </si>
@@ -4211,117 +4209,6 @@
   </si>
   <si>
     <t>Quimicos</t>
-  </si>
-  <si>
-    <t>Estaciones Moose/Scorpion de atornillado e inspección manual (JA100924-03, JA100924-06, JA100924-07, MS-550-03, MS-550-04, MS-550-05, MS-550-06, MS-550-07)</t>
-  </si>
-  <si>
-    <t>29/09/2026</t>
-  </si>
-  <si>
-    <t>Operación normal - verificación Poka Yoke de presencia/orientación de la pieza</t>
-  </si>
-  <si>
-    <t>El sensor/pin Poka Yoke de la fixtura verifica que la pieza esté correctamente orientada antes de permitir el ciclo; el operador puede tener contacto accidental con el mecanismo al cargar la pieza</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>No se requiere EPP adicional; sensores de detección y guarda de protección.</t>
-  </si>
-  <si>
-    <t>SOP Operación estaciones de atornillado manual Moose/Scorpion</t>
-  </si>
-  <si>
-    <t>EHS / Automation</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>Operación normal - lectura de código con escáner fijo</t>
-  </si>
-  <si>
-    <t>El escáner fijo lee el código de la pieza/etiqueta antes o durante el ciclo; el operador puede golpearse con el escáner o golpear material al cargar/descargar</t>
-  </si>
-  <si>
-    <t>Operación normal - contacto con partes fijas de la fixtura (bordes/topes)</t>
-  </si>
-  <si>
-    <t>El operador puede golpearse o atraparse los dedos con los bordes/topes fijos de la fixtura al colocar o retirar la pieza</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>Operación normal - atornillado manual con torque de mano</t>
-  </si>
-  <si>
-    <t>El operador sujeta la pieza en la fixtura y aplica el torque manual con el atornillador; riesgo de atrapamiento/contusión/rasguño con las partes móviles del atornillador</t>
-  </si>
-  <si>
-    <t>Operación normal - islas de conexión eléctrica (alimentación y sensores)</t>
-  </si>
-  <si>
-    <t>Las islas/bloques de conexión eléctrica de alimentación y de sensores quedan accesibles en el área de trabajo durante la operación normal</t>
-  </si>
-  <si>
-    <t>No se requiere EPP adicional; conexiones con guarda de protección, verificar que no presenten aberturas ni cables expuestos.</t>
-  </si>
-  <si>
-    <t>Operación normal - partes neumáticas (pistones de fixtura, en las estaciones que los tienen)</t>
-  </si>
-  <si>
-    <t>Algunas fixturas usan pistones neumáticos para bloqueo de pieza; el operador puede tener contacto con el mecanismo durante la carga/descarga</t>
-  </si>
-  <si>
-    <t>Manejo de materiales - ensamble y atornillado manual repetitivo</t>
-  </si>
-  <si>
-    <t>El operador realiza el ensamble y atornillado de la pieza de forma manual y repetitiva durante el turno</t>
-  </si>
-  <si>
-    <t>No se requiere EPP adicional.</t>
-  </si>
-  <si>
-    <t>Evaluación ergonómica de la estación</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>Mantenimiento correctivo / solución de problemas eléctricos</t>
-  </si>
-  <si>
-    <t>El personal de mantenimiento abre el panel/gabinete eléctrico de la estación para diagnóstico o reparación</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>Guantes dieléctricos (clase según voltaje) y calzado aislante.</t>
-  </si>
-  <si>
-    <t>Procedimiento LOTO de la estación</t>
-  </si>
-  <si>
-    <t>Mantenimiento - energía neumática residual (en las estaciones con pistones de fixtura)</t>
-  </si>
-  <si>
-    <t>El personal de mantenimiento bloquea la válvula de despresurización/bloqueo LOTO neumática antes de intervenir cilindros o líneas de aire</t>
-  </si>
-  <si>
-    <t>No se requiere EPP adicional; válvula de bloqueo/sangrado LOTO neumática dedicada.</t>
-  </si>
-  <si>
-    <t>Mantenimiento al atornillador (bloqueo y etiquetado)</t>
-  </si>
-  <si>
-    <t>El personal de mantenimiento bloquea el switch general de desconexión antes de intervenir el atornillador o la fixtura</t>
-  </si>
-  <si>
-    <t>No se requiere EPP adicional; candado y tarjeta de bloqueo en el switch general.</t>
   </si>
 </sst>
 </file>
@@ -5617,60 +5504,31 @@
     <xf numFmtId="0" fontId="26" fillId="21" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5678,9 +5536,14 @@
     <xf numFmtId="0" fontId="15" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="11" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5691,7 +5554,31 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5737,93 +5624,6 @@
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="20">
-    <dxf>
-      <font>
-        <color theme="6" tint="-0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="2" tint="-0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF2EBB4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="9" tint="-0.24994659260841701"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="6" tint="-0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="2" tint="-0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF2EBB4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="9" tint="-0.24994659260841701"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -5948,6 +5748,93 @@
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <color theme="6" tint="-0.499984740745262"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="2" tint="-0.499984740745262"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF2EBB4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9" tint="-0.24994659260841701"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="6" tint="-0.499984740745262"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="2" tint="-0.499984740745262"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF2EBB4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9" tint="-0.24994659260841701"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -6019,7 +5906,7 @@
 </file>
 
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
-<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <global>
     <keyFlags>
       <key name="_Self">
@@ -6077,7 +5964,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{7E79E3D2-78BB-4383-937E-1693DF7D0F6F}" name="Table4" displayName="Table4" ref="B2:G43" totalsRowShown="0" headerRowDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{7E79E3D2-78BB-4383-937E-1693DF7D0F6F}" name="Table4" displayName="Table4" ref="B2:G43" totalsRowShown="0" headerRowDxfId="10">
   <autoFilter ref="B2:G43" xr:uid="{7E79E3D2-78BB-4383-937E-1693DF7D0F6F}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{0145E517-46C4-42E4-BF24-372761AACB5B}" name="PJ-EHSIP"/>
@@ -6092,20 +5979,20 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table2" displayName="Table2" ref="B2:B33" totalsRowShown="0" headerRowDxfId="18" dataDxfId="16" headerRowBorderDxfId="17" tableBorderDxfId="15" totalsRowBorderDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table2" displayName="Table2" ref="B2:B33" totalsRowShown="0" headerRowDxfId="9" dataDxfId="7" headerRowBorderDxfId="8" tableBorderDxfId="6" totalsRowBorderDxfId="5">
   <autoFilter ref="B2:B33" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Guía de EPP (No definitiva)" dataDxfId="13"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Guía de EPP (No definitiva)" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table1" displayName="Table1" ref="C1:C50" totalsRowShown="0" headerRowDxfId="12" dataDxfId="10" headerRowBorderDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table1" displayName="Table1" ref="C1:C50" totalsRowShown="0" headerRowDxfId="3" dataDxfId="1" headerRowBorderDxfId="2">
   <autoFilter ref="C1:C50" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Guía de EPP (No definitiva)" dataDxfId="9"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Guía de EPP (No definitiva)" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6461,189 +6348,192 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:S33"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27" customWidth="1"/>
-    <col min="3" max="3" width="28.77734375" customWidth="1"/>
-    <col min="4" max="6" width="17" customWidth="1"/>
-    <col min="7" max="7" width="13.109375" customWidth="1"/>
-    <col min="8" max="10" width="7.88671875" customWidth="1"/>
-    <col min="11" max="11" width="38.33203125" customWidth="1"/>
-    <col min="12" max="12" width="38.88671875" customWidth="1"/>
-    <col min="13" max="13" width="36.5546875" customWidth="1"/>
-    <col min="14" max="14" width="13.5546875" customWidth="1"/>
-    <col min="15" max="15" width="11.6640625" customWidth="1"/>
+    <col min="3" max="6" width="17" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" customWidth="1"/>
+    <col min="8" max="10" width="7.85546875" customWidth="1"/>
+    <col min="11" max="11" width="38.28515625" customWidth="1"/>
+    <col min="12" max="12" width="38.85546875" customWidth="1"/>
+    <col min="13" max="13" width="36.5703125" customWidth="1"/>
+    <col min="14" max="14" width="13.5703125" customWidth="1"/>
+    <col min="15" max="15" width="11.7109375" customWidth="1"/>
     <col min="16" max="16" width="8" customWidth="1"/>
-    <col min="17" max="17" width="14.6640625" customWidth="1"/>
-    <col min="18" max="19" width="11.44140625" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" customWidth="1"/>
+    <col min="18" max="19" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="20" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="140" t="s">
+    <row r="1" spans="1:19" s="20" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="126" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="132"/>
-      <c r="C1" s="132"/>
-      <c r="D1" s="133"/>
-      <c r="E1" s="138" t="s">
+      <c r="B1" s="127"/>
+      <c r="C1" s="127"/>
+      <c r="D1" s="128"/>
+      <c r="E1" s="118" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="121"/>
-      <c r="G1" s="122"/>
-      <c r="H1" s="145" t="s">
+      <c r="F1" s="119"/>
+      <c r="G1" s="120"/>
+      <c r="H1" s="135" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="125"/>
-      <c r="J1" s="125"/>
-      <c r="K1" s="125"/>
-      <c r="L1" s="125"/>
-      <c r="M1" s="125"/>
-      <c r="N1" s="125"/>
-      <c r="O1" s="125"/>
-      <c r="P1" s="125"/>
-      <c r="Q1" s="125"/>
-      <c r="R1" s="125"/>
-      <c r="S1" s="126"/>
-    </row>
-    <row r="2" spans="1:19" s="20" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="131" t="s">
-        <v>1242</v>
-      </c>
-      <c r="B2" s="132"/>
-      <c r="C2" s="132"/>
-      <c r="D2" s="133"/>
-      <c r="E2" s="141"/>
-      <c r="F2" s="128"/>
-      <c r="G2" s="142"/>
-      <c r="H2" s="147" t="s">
+      <c r="I1" s="136"/>
+      <c r="J1" s="136"/>
+      <c r="K1" s="136"/>
+      <c r="L1" s="136"/>
+      <c r="M1" s="136"/>
+      <c r="N1" s="136"/>
+      <c r="O1" s="136"/>
+      <c r="P1" s="136"/>
+      <c r="Q1" s="136"/>
+      <c r="R1" s="136"/>
+      <c r="S1" s="137"/>
+    </row>
+    <row r="2" spans="1:19" s="20" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REVALIDACION: Estaciones Moose/Scorpion de atornillado e inspección manual (JA100924-03, JA100924-06, JA100924-07, MS-550-03, MS-550-04, MS-550-05, MS-550-06, MS-550-07)</t>
+        </is>
+      </c>
+      <c r="B2" s="127"/>
+      <c r="C2" s="127"/>
+      <c r="D2" s="128"/>
+      <c r="E2" s="129"/>
+      <c r="F2" s="130"/>
+      <c r="G2" s="131"/>
+      <c r="H2" s="139" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="121"/>
-      <c r="J2" s="121"/>
-      <c r="K2" s="121"/>
+      <c r="I2" s="119"/>
+      <c r="J2" s="119"/>
+      <c r="K2" s="119"/>
       <c r="L2" s="22" t="s">
         <v>4</v>
       </c>
       <c r="M2" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="123" t="s">
+      <c r="N2" s="149" t="s">
         <v>5</v>
       </c>
-      <c r="O2" s="122"/>
-      <c r="P2" s="123" t="s">
+      <c r="O2" s="120"/>
+      <c r="P2" s="149" t="s">
         <v>5</v>
       </c>
-      <c r="Q2" s="121"/>
-      <c r="R2" s="121"/>
-      <c r="S2" s="122"/>
-    </row>
-    <row r="3" spans="1:19" s="20" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="144" t="s">
+      <c r="Q2" s="119"/>
+      <c r="R2" s="119"/>
+      <c r="S2" s="120"/>
+    </row>
+    <row r="3" spans="1:19" s="20" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="133" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="132"/>
-      <c r="C3" s="132"/>
-      <c r="D3" s="52" t="s">
-        <v>1243</v>
-      </c>
-      <c r="E3" s="150" t="s">
+      <c r="B3" s="127"/>
+      <c r="C3" s="127"/>
+      <c r="D3" s="52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30/09/2026</t>
+        </is>
+      </c>
+      <c r="E3" s="143" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="132"/>
-      <c r="G3" s="132"/>
-      <c r="H3" s="127"/>
-      <c r="I3" s="128"/>
-      <c r="J3" s="128"/>
-      <c r="K3" s="128"/>
+      <c r="F3" s="127"/>
+      <c r="G3" s="127"/>
+      <c r="H3" s="150"/>
+      <c r="I3" s="130"/>
+      <c r="J3" s="130"/>
+      <c r="K3" s="130"/>
       <c r="L3" s="21"/>
       <c r="M3" s="50"/>
-      <c r="N3" s="129"/>
-      <c r="O3" s="121"/>
-      <c r="P3" s="120"/>
-      <c r="Q3" s="121"/>
-      <c r="R3" s="121"/>
-      <c r="S3" s="122"/>
-    </row>
-    <row r="4" spans="1:19" s="20" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="132"/>
-      <c r="B4" s="132"/>
-      <c r="C4" s="132"/>
+      <c r="N3" s="144"/>
+      <c r="O3" s="119"/>
+      <c r="P3" s="148"/>
+      <c r="Q3" s="119"/>
+      <c r="R3" s="119"/>
+      <c r="S3" s="120"/>
+    </row>
+    <row r="4" spans="1:19" s="20" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="127"/>
+      <c r="B4" s="127"/>
+      <c r="C4" s="127"/>
       <c r="D4" s="52"/>
-      <c r="E4" s="132"/>
-      <c r="F4" s="132"/>
-      <c r="G4" s="132"/>
-      <c r="H4" s="137" t="s">
+      <c r="E4" s="127"/>
+      <c r="F4" s="127"/>
+      <c r="G4" s="127"/>
+      <c r="H4" s="147" t="s">
         <v>8</v>
       </c>
-      <c r="I4" s="125"/>
-      <c r="J4" s="125"/>
-      <c r="K4" s="125"/>
+      <c r="I4" s="136"/>
+      <c r="J4" s="136"/>
+      <c r="K4" s="136"/>
       <c r="L4" s="23" t="s">
         <v>9</v>
       </c>
       <c r="M4" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="N4" s="124" t="s">
+      <c r="N4" s="142" t="s">
         <v>5</v>
       </c>
-      <c r="O4" s="126"/>
-      <c r="P4" s="124" t="s">
+      <c r="O4" s="137"/>
+      <c r="P4" s="142" t="s">
         <v>5</v>
       </c>
-      <c r="Q4" s="125"/>
-      <c r="R4" s="125"/>
-      <c r="S4" s="126"/>
-    </row>
-    <row r="5" spans="1:19" s="20" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="139">
+      <c r="Q4" s="136"/>
+      <c r="R4" s="136"/>
+      <c r="S4" s="137"/>
+    </row>
+    <row r="5" spans="1:19" s="20" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="123">
         <f ca="1">TODAY()</f>
-        <v>46294</v>
-      </c>
-      <c r="B5" s="135"/>
-      <c r="C5" s="135"/>
-      <c r="D5" s="136"/>
-      <c r="E5" s="134">
+        <v>46069</v>
+      </c>
+      <c r="B5" s="124"/>
+      <c r="C5" s="124"/>
+      <c r="D5" s="125"/>
+      <c r="E5" s="146">
         <f ca="1">A5+365</f>
-        <v>46659</v>
-      </c>
-      <c r="F5" s="135"/>
-      <c r="G5" s="136"/>
-      <c r="H5" s="129"/>
-      <c r="I5" s="121"/>
-      <c r="J5" s="121"/>
-      <c r="K5" s="121"/>
+        <v>46434</v>
+      </c>
+      <c r="F5" s="124"/>
+      <c r="G5" s="125"/>
+      <c r="H5" s="144"/>
+      <c r="I5" s="119"/>
+      <c r="J5" s="119"/>
+      <c r="K5" s="119"/>
       <c r="L5" s="50"/>
       <c r="M5" s="21"/>
-      <c r="N5" s="129"/>
-      <c r="O5" s="121"/>
-      <c r="P5" s="120"/>
-      <c r="Q5" s="121"/>
-      <c r="R5" s="121"/>
-      <c r="S5" s="122"/>
-    </row>
-    <row r="6" spans="1:19" ht="53.1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="143" t="s">
+      <c r="N5" s="144"/>
+      <c r="O5" s="119"/>
+      <c r="P5" s="148"/>
+      <c r="Q5" s="119"/>
+      <c r="R5" s="119"/>
+      <c r="S5" s="120"/>
+    </row>
+    <row r="6" spans="1:19" ht="53.1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="132" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="118" t="s">
+      <c r="B6" s="121" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="130" t="s">
+      <c r="C6" s="134" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="146" t="s">
+      <c r="D6" s="138" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="130" t="s">
+      <c r="E6" s="134" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="130" t="s">
+      <c r="F6" s="134" t="s">
         <v>15</v>
       </c>
-      <c r="G6" s="130" t="s">
+      <c r="G6" s="134" t="s">
         <v>16</v>
       </c>
       <c r="H6" s="64" t="s">
@@ -6651,16 +6541,16 @@
       </c>
       <c r="I6" s="65"/>
       <c r="J6" s="66"/>
-      <c r="K6" s="118" t="s">
+      <c r="K6" s="121" t="s">
         <v>18</v>
       </c>
-      <c r="L6" s="118" t="s">
+      <c r="L6" s="121" t="s">
         <v>19</v>
       </c>
-      <c r="M6" s="118" t="s">
+      <c r="M6" s="121" t="s">
         <v>20</v>
       </c>
-      <c r="N6" s="118" t="s">
+      <c r="N6" s="121" t="s">
         <v>21</v>
       </c>
       <c r="O6" s="67" t="s">
@@ -6668,21 +6558,21 @@
       </c>
       <c r="P6" s="68"/>
       <c r="Q6" s="69"/>
-      <c r="R6" s="148" t="s">
+      <c r="R6" s="140" t="s">
         <v>23</v>
       </c>
-      <c r="S6" s="118" t="s">
+      <c r="S6" s="121" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="39" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="119"/>
-      <c r="B7" s="119"/>
-      <c r="C7" s="119"/>
-      <c r="D7" s="119"/>
-      <c r="E7" s="119"/>
-      <c r="F7" s="119"/>
-      <c r="G7" s="119"/>
+    <row r="7" spans="1:19" ht="39" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="122"/>
+      <c r="B7" s="122"/>
+      <c r="C7" s="122"/>
+      <c r="D7" s="122"/>
+      <c r="E7" s="122"/>
+      <c r="F7" s="122"/>
+      <c r="G7" s="122"/>
       <c r="H7" s="70" t="s">
         <v>25</v>
       </c>
@@ -6692,10 +6582,10 @@
       <c r="J7" s="70" t="s">
         <v>27</v>
       </c>
-      <c r="K7" s="119"/>
-      <c r="L7" s="119"/>
-      <c r="M7" s="119"/>
-      <c r="N7" s="119"/>
+      <c r="K7" s="122"/>
+      <c r="L7" s="122"/>
+      <c r="M7" s="122"/>
+      <c r="N7" s="122"/>
       <c r="O7" s="63" t="s">
         <v>28</v>
       </c>
@@ -6705,59 +6595,94 @@
       <c r="Q7" s="62" t="s">
         <v>30</v>
       </c>
-      <c r="R7" s="149"/>
-      <c r="S7" s="119"/>
-    </row>
-    <row r="8" spans="1:19" s="19" customFormat="1" ht="158.4" x14ac:dyDescent="0.25">
-      <c r="A8" s="55" t="s">
-        <v>466</v>
-      </c>
-      <c r="B8" s="55" t="s">
-        <v>1244</v>
-      </c>
-      <c r="C8" s="56" t="s">
-        <v>1245</v>
-      </c>
-      <c r="D8" s="56" t="s">
-        <v>200</v>
-      </c>
-      <c r="E8" s="49" t="s">
-        <v>259</v>
-      </c>
-      <c r="F8" s="49" t="s">
-        <v>1054</v>
-      </c>
-      <c r="G8" s="56" t="s">
-        <v>470</v>
-      </c>
-      <c r="H8" s="57" t="s">
-        <v>1246</v>
-      </c>
-      <c r="I8" s="57" t="s">
-        <v>1246</v>
+      <c r="R7" s="141"/>
+      <c r="S7" s="122"/>
+    </row>
+    <row r="8" spans="1:19" s="19" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rutinario</t>
+        </is>
+      </c>
+      <c r="B8" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Carga y atornillado manual de la pieza en la fixtura</t>
+        </is>
+      </c>
+      <c r="C8" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paso 1 de 4: el operador toma la pieza y la coloca en la fixtura</t>
+        </is>
+      </c>
+      <c r="D8" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mecanico</t>
+        </is>
+      </c>
+      <c r="E8" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partes móviles</t>
+        </is>
+      </c>
+      <c r="F8" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Atrapamiento</t>
+        </is>
+      </c>
+      <c r="G8" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control</t>
+        </is>
+      </c>
+      <c r="H8" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I8" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
       </c>
       <c r="J8" s="51">
         <f t="shared" ref="J8" si="0">H8*I8</f>
-        <v>1</v>
-      </c>
-      <c r="K8" s="107" t="s">
-        <v>633</v>
-      </c>
-      <c r="L8" s="58" t="s">
-        <v>1247</v>
-      </c>
-      <c r="M8" s="58" t="s">
-        <v>1248</v>
-      </c>
-      <c r="N8" s="57" t="s">
-        <v>1249</v>
-      </c>
-      <c r="O8" s="49" t="s">
-        <v>1250</v>
+        <v>0</v>
+      </c>
+      <c r="K8" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resguardos mecánicos</t>
+        </is>
+      </c>
+      <c r="L8" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
+        </is>
+      </c>
+      <c r="M8" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16-AT40-3318-00008
+16-AT40-3318-00009
+16-AT40-3318-00010
+16-AT40-3318-00011
+16-AT40-3318-00021
+16-AT40-3318-00024
+16-AT40-3318-00025
+(Front Assy Moose: numero de AV pendiente de confirmar, ilegible en la imagen enviada)</t>
+        </is>
+      </c>
+      <c r="N8" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O8" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
       </c>
       <c r="P8" s="61">
         <f t="shared" ref="P8" si="1">IF(O8=5,(J8*1),IF(O8=4,(J8*0.85),IF(O8=3,(J8*0.15),IF(O8=2,(J8*0.05),IF(O8=1,(J8*-0.0000000000000001),(J8*1))))))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="60">
         <f t="shared" ref="Q8" si="2">IF(J8=0,0,(P8-J8)/J8)</f>
@@ -6766,56 +6691,91 @@
       <c r="R8" s="57"/>
       <c r="S8" s="57"/>
     </row>
-    <row r="9" spans="1:19" s="19" customFormat="1" ht="118.8" x14ac:dyDescent="0.25">
-      <c r="A9" s="55" t="s">
-        <v>466</v>
-      </c>
-      <c r="B9" s="55" t="s">
-        <v>1251</v>
-      </c>
-      <c r="C9" s="56" t="s">
-        <v>1252</v>
-      </c>
-      <c r="D9" s="56" t="s">
-        <v>200</v>
-      </c>
-      <c r="E9" s="49" t="s">
-        <v>259</v>
-      </c>
-      <c r="F9" s="49" t="s">
-        <v>1054</v>
-      </c>
-      <c r="G9" s="56" t="s">
-        <v>470</v>
-      </c>
-      <c r="H9" s="57" t="s">
-        <v>1246</v>
-      </c>
-      <c r="I9" s="57" t="s">
-        <v>1246</v>
+    <row r="9" spans="1:19" s="19" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rutinario</t>
+        </is>
+      </c>
+      <c r="B9" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Carga y atornillado manual de la pieza en la fixtura</t>
+        </is>
+      </c>
+      <c r="C9" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paso 2 de 4: asegura la pieza con el seguro/clip manual de la fixtura (Partes Fijas)</t>
+        </is>
+      </c>
+      <c r="D9" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mecanico</t>
+        </is>
+      </c>
+      <c r="E9" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partes móviles</t>
+        </is>
+      </c>
+      <c r="F9" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Laceración</t>
+        </is>
+      </c>
+      <c r="G9" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control</t>
+        </is>
+      </c>
+      <c r="H9" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I9" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
       </c>
       <c r="J9" s="51">
         <f t="shared" ref="J9:J27" si="3">H9*I9</f>
-        <v>1</v>
-      </c>
-      <c r="K9" s="107" t="s">
-        <v>633</v>
-      </c>
-      <c r="L9" s="58" t="s">
-        <v>1247</v>
-      </c>
-      <c r="M9" s="58" t="s">
-        <v>1248</v>
-      </c>
-      <c r="N9" s="57" t="s">
-        <v>1249</v>
-      </c>
-      <c r="O9" s="49" t="s">
-        <v>1250</v>
+        <v>0</v>
+      </c>
+      <c r="K9" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resguardos mecánicos</t>
+        </is>
+      </c>
+      <c r="L9" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
+        </is>
+      </c>
+      <c r="M9" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16-AT40-3318-00008
+16-AT40-3318-00009
+16-AT40-3318-00010
+16-AT40-3318-00011
+16-AT40-3318-00021
+16-AT40-3318-00024
+16-AT40-3318-00025
+(Front Assy Moose: numero de AV pendiente de confirmar, ilegible en la imagen enviada)</t>
+        </is>
+      </c>
+      <c r="N9" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O9" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
       </c>
       <c r="P9" s="61">
         <f t="shared" ref="P9:P27" si="4">IF(O9=5,(J9*1),IF(O9=4,(J9*0.85),IF(O9=3,(J9*0.15),IF(O9=2,(J9*0.05),IF(O9=1,(J9*-0.0000000000000001),(J9*1))))))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="60">
         <f t="shared" ref="Q9:Q27" si="5">IF(J9=0,0,(P9-J9)/J9)</f>
@@ -6824,56 +6784,91 @@
       <c r="R9" s="57"/>
       <c r="S9" s="57"/>
     </row>
-    <row r="10" spans="1:19" s="19" customFormat="1" ht="105.6" x14ac:dyDescent="0.25">
-      <c r="A10" s="55" t="s">
-        <v>466</v>
-      </c>
-      <c r="B10" s="55" t="s">
-        <v>1253</v>
-      </c>
-      <c r="C10" s="56" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D10" s="56" t="s">
-        <v>200</v>
-      </c>
-      <c r="E10" s="49" t="s">
-        <v>259</v>
-      </c>
-      <c r="F10" s="49" t="s">
-        <v>216</v>
-      </c>
-      <c r="G10" s="56" t="s">
-        <v>470</v>
-      </c>
-      <c r="H10" s="57" t="s">
-        <v>1246</v>
-      </c>
-      <c r="I10" s="57" t="s">
-        <v>1255</v>
+    <row r="10" spans="1:19" s="19" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rutinario</t>
+        </is>
+      </c>
+      <c r="B10" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Carga y atornillado manual de la pieza en la fixtura</t>
+        </is>
+      </c>
+      <c r="C10" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paso 3 de 4: toma el atornillador manual y aplica el torque en los puntos programados</t>
+        </is>
+      </c>
+      <c r="D10" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mecanico</t>
+        </is>
+      </c>
+      <c r="E10" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partes móviles</t>
+        </is>
+      </c>
+      <c r="F10" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Laceración</t>
+        </is>
+      </c>
+      <c r="G10" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control</t>
+        </is>
+      </c>
+      <c r="H10" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="I10" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
       </c>
       <c r="J10" s="51">
         <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="K10" s="107" t="s">
-        <v>633</v>
-      </c>
-      <c r="L10" s="58" t="s">
-        <v>1247</v>
-      </c>
-      <c r="M10" s="58" t="s">
-        <v>1248</v>
-      </c>
-      <c r="N10" s="57" t="s">
-        <v>1249</v>
-      </c>
-      <c r="O10" s="49" t="s">
-        <v>1250</v>
+        <v>0</v>
+      </c>
+      <c r="K10" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resguardos mecánicos</t>
+        </is>
+      </c>
+      <c r="L10" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
+        </is>
+      </c>
+      <c r="M10" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16-AT40-3318-00008
+16-AT40-3318-00009
+16-AT40-3318-00010
+16-AT40-3318-00011
+16-AT40-3318-00021
+16-AT40-3318-00024
+16-AT40-3318-00025
+(Front Assy Moose: numero de AV pendiente de confirmar, ilegible en la imagen enviada)</t>
+        </is>
+      </c>
+      <c r="N10" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O10" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
       </c>
       <c r="P10" s="61">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="60">
         <f t="shared" si="5"/>
@@ -6882,56 +6877,91 @@
       <c r="R10" s="57"/>
       <c r="S10" s="57"/>
     </row>
-    <row r="11" spans="1:19" s="19" customFormat="1" ht="132" x14ac:dyDescent="0.25">
-      <c r="A11" s="55" t="s">
-        <v>466</v>
-      </c>
-      <c r="B11" s="55" t="s">
-        <v>1256</v>
-      </c>
-      <c r="C11" s="56" t="s">
-        <v>1257</v>
-      </c>
-      <c r="D11" s="56" t="s">
-        <v>200</v>
-      </c>
-      <c r="E11" s="49" t="s">
-        <v>259</v>
-      </c>
-      <c r="F11" s="49" t="s">
-        <v>216</v>
-      </c>
-      <c r="G11" s="56" t="s">
-        <v>470</v>
-      </c>
-      <c r="H11" s="57" t="s">
-        <v>1255</v>
-      </c>
-      <c r="I11" s="57" t="s">
-        <v>1255</v>
+    <row r="11" spans="1:19" s="19" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rutinario</t>
+        </is>
+      </c>
+      <c r="B11" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Carga y atornillado manual de la pieza en la fixtura</t>
+        </is>
+      </c>
+      <c r="C11" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paso 4 de 4: retira la pieza terminada de la fixtura y la coloca en el contenedor de salida</t>
+        </is>
+      </c>
+      <c r="D11" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ergonomía</t>
+        </is>
+      </c>
+      <c r="E11" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Movimientos repetitivos</t>
+        </is>
+      </c>
+      <c r="F11" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fatiga muscular</t>
+        </is>
+      </c>
+      <c r="G11" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Influencia</t>
+        </is>
+      </c>
+      <c r="H11" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="I11" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
       </c>
       <c r="J11" s="51">
         <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="K11" s="107" t="s">
-        <v>633</v>
-      </c>
-      <c r="L11" s="58" t="s">
-        <v>1247</v>
-      </c>
-      <c r="M11" s="58" t="s">
-        <v>1248</v>
-      </c>
-      <c r="N11" s="57" t="s">
-        <v>1249</v>
-      </c>
-      <c r="O11" s="49" t="s">
-        <v>1250</v>
+        <v>0</v>
+      </c>
+      <c r="K11" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ergonomía</t>
+        </is>
+      </c>
+      <c r="L11" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
+        </is>
+      </c>
+      <c r="M11" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16-AT40-3318-00008
+16-AT40-3318-00009
+16-AT40-3318-00010
+16-AT40-3318-00011
+16-AT40-3318-00021
+16-AT40-3318-00024
+16-AT40-3318-00025
+(Front Assy Moose: numero de AV pendiente de confirmar, ilegible en la imagen enviada)</t>
+        </is>
+      </c>
+      <c r="N11" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O11" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
       </c>
       <c r="P11" s="61">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q11" s="60">
         <f t="shared" si="5"/>
@@ -6940,56 +6970,91 @@
       <c r="R11" s="57"/>
       <c r="S11" s="57"/>
     </row>
-    <row r="12" spans="1:19" ht="118.8" x14ac:dyDescent="0.25">
-      <c r="A12" s="55" t="s">
-        <v>466</v>
-      </c>
-      <c r="B12" s="55" t="s">
-        <v>1258</v>
-      </c>
-      <c r="C12" s="56" t="s">
-        <v>1259</v>
-      </c>
-      <c r="D12" s="56" t="s">
-        <v>356</v>
-      </c>
-      <c r="E12" s="49" t="s">
-        <v>357</v>
-      </c>
-      <c r="F12" s="49" t="s">
-        <v>358</v>
-      </c>
-      <c r="G12" s="56" t="s">
-        <v>470</v>
-      </c>
-      <c r="H12" s="57" t="s">
-        <v>1255</v>
-      </c>
-      <c r="I12" s="57" t="s">
-        <v>1246</v>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A12" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rutinario</t>
+        </is>
+      </c>
+      <c r="B12" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verificación Poka Yoke de presencia/orientación de la pieza</t>
+        </is>
+      </c>
+      <c r="C12" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El sensor/pin Poka Yoke de la fixtura verifica que la pieza esté correctamente orientada antes de permitir el ciclo; el operador puede tener contacto accidental con el mecanismo al cargar la pieza</t>
+        </is>
+      </c>
+      <c r="D12" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mecanico</t>
+        </is>
+      </c>
+      <c r="E12" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partes móviles</t>
+        </is>
+      </c>
+      <c r="F12" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Laceración</t>
+        </is>
+      </c>
+      <c r="G12" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control</t>
+        </is>
+      </c>
+      <c r="H12" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I12" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
       </c>
       <c r="J12" s="51">
         <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="K12" s="107" t="s">
-        <v>677</v>
-      </c>
-      <c r="L12" s="58" t="s">
-        <v>1260</v>
-      </c>
-      <c r="M12" s="58" t="s">
-        <v>1248</v>
-      </c>
-      <c r="N12" s="57" t="s">
-        <v>1249</v>
-      </c>
-      <c r="O12" s="49" t="s">
-        <v>1250</v>
+        <v>0</v>
+      </c>
+      <c r="K12" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resguardos mecánicos</t>
+        </is>
+      </c>
+      <c r="L12" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
+        </is>
+      </c>
+      <c r="M12" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16-AT40-3318-00008
+16-AT40-3318-00009
+16-AT40-3318-00010
+16-AT40-3318-00011
+16-AT40-3318-00021
+16-AT40-3318-00024
+16-AT40-3318-00025
+(Front Assy Moose: numero de AV pendiente de confirmar, ilegible en la imagen enviada)</t>
+        </is>
+      </c>
+      <c r="N12" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O12" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
       </c>
       <c r="P12" s="61">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q12" s="60">
         <f t="shared" si="5"/>
@@ -6998,56 +7063,91 @@
       <c r="R12" s="57"/>
       <c r="S12" s="57"/>
     </row>
-    <row r="13" spans="1:19" ht="118.8" x14ac:dyDescent="0.25">
-      <c r="A13" s="55" t="s">
-        <v>466</v>
-      </c>
-      <c r="B13" s="55" t="s">
-        <v>1261</v>
-      </c>
-      <c r="C13" s="56" t="s">
-        <v>1262</v>
-      </c>
-      <c r="D13" s="56" t="s">
-        <v>200</v>
-      </c>
-      <c r="E13" s="49" t="s">
-        <v>259</v>
-      </c>
-      <c r="F13" s="49" t="s">
-        <v>216</v>
-      </c>
-      <c r="G13" s="56" t="s">
-        <v>470</v>
-      </c>
-      <c r="H13" s="57" t="s">
-        <v>1255</v>
-      </c>
-      <c r="I13" s="57" t="s">
-        <v>1255</v>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A13" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rutinario</t>
+        </is>
+      </c>
+      <c r="B13" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lectura de código con escáner fijo</t>
+        </is>
+      </c>
+      <c r="C13" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El escáner fijo lee el código de la pieza/etiqueta antes o durante el ciclo; el operador puede golpearse con el escáner o golpear material al cargar/descargar</t>
+        </is>
+      </c>
+      <c r="D13" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mecanico</t>
+        </is>
+      </c>
+      <c r="E13" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partes móviles</t>
+        </is>
+      </c>
+      <c r="F13" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Laceración</t>
+        </is>
+      </c>
+      <c r="G13" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control</t>
+        </is>
+      </c>
+      <c r="H13" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I13" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
       </c>
       <c r="J13" s="51">
         <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="K13" s="107" t="s">
-        <v>744</v>
-      </c>
-      <c r="L13" s="58" t="s">
-        <v>1247</v>
-      </c>
-      <c r="M13" s="58" t="s">
-        <v>1248</v>
-      </c>
-      <c r="N13" s="57" t="s">
-        <v>1249</v>
-      </c>
-      <c r="O13" s="49" t="s">
-        <v>1250</v>
+        <v>0</v>
+      </c>
+      <c r="K13" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resguardos mecánicos</t>
+        </is>
+      </c>
+      <c r="L13" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
+        </is>
+      </c>
+      <c r="M13" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16-AT40-3318-00008
+16-AT40-3318-00009
+16-AT40-3318-00010
+16-AT40-3318-00011
+16-AT40-3318-00021
+16-AT40-3318-00024
+16-AT40-3318-00025
+(Front Assy Moose: numero de AV pendiente de confirmar, ilegible en la imagen enviada)</t>
+        </is>
+      </c>
+      <c r="N13" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O13" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
       </c>
       <c r="P13" s="61">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q13" s="60">
         <f t="shared" si="5"/>
@@ -7056,56 +7156,91 @@
       <c r="R13" s="57"/>
       <c r="S13" s="57"/>
     </row>
-    <row r="14" spans="1:19" ht="79.2" x14ac:dyDescent="0.25">
-      <c r="A14" s="55" t="s">
-        <v>466</v>
-      </c>
-      <c r="B14" s="55" t="s">
-        <v>1263</v>
-      </c>
-      <c r="C14" s="56" t="s">
-        <v>1264</v>
-      </c>
-      <c r="D14" s="56" t="s">
-        <v>397</v>
-      </c>
-      <c r="E14" s="49" t="s">
-        <v>404</v>
-      </c>
-      <c r="F14" s="49" t="s">
-        <v>1026</v>
-      </c>
-      <c r="G14" s="56" t="s">
-        <v>471</v>
-      </c>
-      <c r="H14" s="57" t="s">
-        <v>1255</v>
-      </c>
-      <c r="I14" s="57" t="s">
-        <v>1250</v>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A14" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rutinario</t>
+        </is>
+      </c>
+      <c r="B14" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Islas de conexión eléctrica (alimentación y sensores)</t>
+        </is>
+      </c>
+      <c r="C14" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Las islas/bloques de conexión eléctrica de alimentación y de sensores quedan accesibles en el área de trabajo durante la operación normal</t>
+        </is>
+      </c>
+      <c r="D14" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eléctrico</t>
+        </is>
+      </c>
+      <c r="E14" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Conductores energizados</t>
+        </is>
+      </c>
+      <c r="F14" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Electrocución</t>
+        </is>
+      </c>
+      <c r="G14" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control</t>
+        </is>
+      </c>
+      <c r="H14" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="I14" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
       </c>
       <c r="J14" s="51">
         <f t="shared" si="3"/>
-        <v>6</v>
-      </c>
-      <c r="K14" s="107" t="s">
-        <v>681</v>
-      </c>
-      <c r="L14" s="58" t="s">
-        <v>1265</v>
-      </c>
-      <c r="M14" s="58" t="s">
-        <v>1266</v>
-      </c>
-      <c r="N14" s="57" t="s">
-        <v>1249</v>
-      </c>
-      <c r="O14" s="49" t="s">
-        <v>1267</v>
+        <v>0</v>
+      </c>
+      <c r="K14" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">detección de voltaje</t>
+        </is>
+      </c>
+      <c r="L14" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7. Adicional para intervención eléctrica: guantes dieléctricos (clase según voltaje) y calzado aislante.</t>
+        </is>
+      </c>
+      <c r="M14" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16-AT40-3318-00008
+16-AT40-3318-00009
+16-AT40-3318-00010
+16-AT40-3318-00011
+16-AT40-3318-00021
+16-AT40-3318-00024
+16-AT40-3318-00025
+(Front Assy Moose: numero de AV pendiente de confirmar, ilegible en la imagen enviada)</t>
+        </is>
+      </c>
+      <c r="N14" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O14" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
       </c>
       <c r="P14" s="61">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q14" s="60">
         <f t="shared" si="5"/>
@@ -7114,56 +7249,91 @@
       <c r="R14" s="57"/>
       <c r="S14" s="57"/>
     </row>
-    <row r="15" spans="1:19" ht="92.4" x14ac:dyDescent="0.25">
-      <c r="A15" s="55" t="s">
-        <v>467</v>
-      </c>
-      <c r="B15" s="55" t="s">
-        <v>1268</v>
-      </c>
-      <c r="C15" s="56" t="s">
-        <v>1269</v>
-      </c>
-      <c r="D15" s="56" t="s">
-        <v>356</v>
-      </c>
-      <c r="E15" s="49" t="s">
-        <v>357</v>
-      </c>
-      <c r="F15" s="49" t="s">
-        <v>358</v>
-      </c>
-      <c r="G15" s="56" t="s">
-        <v>470</v>
-      </c>
-      <c r="H15" s="57" t="s">
-        <v>1270</v>
-      </c>
-      <c r="I15" s="57" t="s">
-        <v>1255</v>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A15" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rutinario</t>
+        </is>
+      </c>
+      <c r="B15" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contacto con partes neumáticas (pistones de fixtura, en las estaciones que los tienen)</t>
+        </is>
+      </c>
+      <c r="C15" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Algunas fixturas usan pistones neumáticos para bloqueo de pieza; el operador puede tener contacto con el mecanismo durante la carga/descarga</t>
+        </is>
+      </c>
+      <c r="D15" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mecanico</t>
+        </is>
+      </c>
+      <c r="E15" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partes móviles</t>
+        </is>
+      </c>
+      <c r="F15" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Atrapamiento</t>
+        </is>
+      </c>
+      <c r="G15" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control</t>
+        </is>
+      </c>
+      <c r="H15" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="I15" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
       </c>
       <c r="J15" s="51">
         <f t="shared" si="3"/>
-        <v>10</v>
-      </c>
-      <c r="K15" s="107" t="s">
-        <v>605</v>
-      </c>
-      <c r="L15" s="58" t="s">
-        <v>1271</v>
-      </c>
-      <c r="M15" s="58" t="s">
-        <v>1272</v>
-      </c>
-      <c r="N15" s="57" t="s">
-        <v>1249</v>
-      </c>
-      <c r="O15" s="49" t="s">
-        <v>1267</v>
+        <v>0</v>
+      </c>
+      <c r="K15" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sensores</t>
+        </is>
+      </c>
+      <c r="L15" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
+        </is>
+      </c>
+      <c r="M15" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16-AT40-3318-00008
+16-AT40-3318-00009
+16-AT40-3318-00010
+16-AT40-3318-00011
+16-AT40-3318-00021
+16-AT40-3318-00024
+16-AT40-3318-00025
+(Front Assy Moose: numero de AV pendiente de confirmar, ilegible en la imagen enviada)</t>
+        </is>
+      </c>
+      <c r="N15" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O15" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
       </c>
       <c r="P15" s="61">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q15" s="60">
         <f t="shared" si="5"/>
@@ -7172,56 +7342,91 @@
       <c r="R15" s="57"/>
       <c r="S15" s="57"/>
     </row>
-    <row r="16" spans="1:19" ht="118.8" x14ac:dyDescent="0.25">
-      <c r="A16" s="55" t="s">
-        <v>467</v>
-      </c>
-      <c r="B16" s="55" t="s">
-        <v>1273</v>
-      </c>
-      <c r="C16" s="56" t="s">
-        <v>1274</v>
-      </c>
-      <c r="D16" s="56" t="s">
-        <v>200</v>
-      </c>
-      <c r="E16" s="49" t="s">
-        <v>249</v>
-      </c>
-      <c r="F16" s="49" t="s">
-        <v>1050</v>
-      </c>
-      <c r="G16" s="56" t="s">
-        <v>470</v>
-      </c>
-      <c r="H16" s="57" t="s">
-        <v>1255</v>
-      </c>
-      <c r="I16" s="57" t="s">
-        <v>1246</v>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A16" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rutinario</t>
+        </is>
+      </c>
+      <c r="B16" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abastecimiento de material e insumos (tornillos, piezas)</t>
+        </is>
+      </c>
+      <c r="C16" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El operador retira el contenedor/charola vacía y coloca uno nuevo con tornillos o piezas de entrada</t>
+        </is>
+      </c>
+      <c r="D16" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ergonomía</t>
+        </is>
+      </c>
+      <c r="E16" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Levantamiento manual</t>
+        </is>
+      </c>
+      <c r="F16" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lumbalgia</t>
+        </is>
+      </c>
+      <c r="G16" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Influencia</t>
+        </is>
+      </c>
+      <c r="H16" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="I16" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
       </c>
       <c r="J16" s="51">
         <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="K16" s="107" t="s">
-        <v>647</v>
-      </c>
-      <c r="L16" s="58" t="s">
-        <v>1275</v>
-      </c>
-      <c r="M16" s="58" t="s">
-        <v>1272</v>
-      </c>
-      <c r="N16" s="57" t="s">
-        <v>1249</v>
-      </c>
-      <c r="O16" s="49" t="s">
-        <v>1250</v>
+        <v>0</v>
+      </c>
+      <c r="K16" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Técnica adecuada</t>
+        </is>
+      </c>
+      <c r="L16" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
+        </is>
+      </c>
+      <c r="M16" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16-AT40-3318-00008
+16-AT40-3318-00009
+16-AT40-3318-00010
+16-AT40-3318-00011
+16-AT40-3318-00021
+16-AT40-3318-00024
+16-AT40-3318-00025
+(Front Assy Moose: numero de AV pendiente de confirmar, ilegible en la imagen enviada)</t>
+        </is>
+      </c>
+      <c r="N16" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O16" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
       </c>
       <c r="P16" s="61">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="60">
         <f t="shared" si="5"/>
@@ -7230,56 +7435,91 @@
       <c r="R16" s="57"/>
       <c r="S16" s="57"/>
     </row>
-    <row r="17" spans="1:19" ht="105.6" x14ac:dyDescent="0.25">
-      <c r="A17" s="55" t="s">
-        <v>467</v>
-      </c>
-      <c r="B17" s="55" t="s">
-        <v>1276</v>
-      </c>
-      <c r="C17" s="56" t="s">
-        <v>1277</v>
-      </c>
-      <c r="D17" s="56" t="s">
-        <v>200</v>
-      </c>
-      <c r="E17" s="49" t="s">
-        <v>259</v>
-      </c>
-      <c r="F17" s="49" t="s">
-        <v>216</v>
-      </c>
-      <c r="G17" s="56" t="s">
-        <v>470</v>
-      </c>
-      <c r="H17" s="57" t="s">
-        <v>1246</v>
-      </c>
-      <c r="I17" s="57" t="s">
-        <v>1246</v>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A17" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No rutinario</t>
+        </is>
+      </c>
+      <c r="B17" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Arranque de la estación al inicio de turno</t>
+        </is>
+      </c>
+      <c r="C17" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paso 1 de 2: energiza el switch general de la estación</t>
+        </is>
+      </c>
+      <c r="D17" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eléctrico</t>
+        </is>
+      </c>
+      <c r="E17" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Conductores energizados</t>
+        </is>
+      </c>
+      <c r="F17" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Electrocución</t>
+        </is>
+      </c>
+      <c r="G17" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control</t>
+        </is>
+      </c>
+      <c r="H17" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="I17" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
       </c>
       <c r="J17" s="51">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="K17" s="107" t="s">
-        <v>605</v>
-      </c>
-      <c r="L17" s="58" t="s">
-        <v>1278</v>
-      </c>
-      <c r="M17" s="58" t="s">
-        <v>1272</v>
-      </c>
-      <c r="N17" s="57" t="s">
-        <v>1249</v>
-      </c>
-      <c r="O17" s="49" t="s">
-        <v>1267</v>
+        <v>0</v>
+      </c>
+      <c r="K17" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOTO</t>
+        </is>
+      </c>
+      <c r="L17" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7. Adicional para intervención eléctrica: guantes dieléctricos (clase según voltaje) y calzado aislante.</t>
+        </is>
+      </c>
+      <c r="M17" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16-AT40-3318-00008
+16-AT40-3318-00009
+16-AT40-3318-00010
+16-AT40-3318-00011
+16-AT40-3318-00021
+16-AT40-3318-00024
+16-AT40-3318-00025
+(Front Assy Moose: numero de AV pendiente de confirmar, ilegible en la imagen enviada)</t>
+        </is>
+      </c>
+      <c r="N17" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O17" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
       </c>
       <c r="P17" s="61">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q17" s="60">
         <f t="shared" si="5"/>
@@ -7288,25 +7528,88 @@
       <c r="R17" s="57"/>
       <c r="S17" s="57"/>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A18" s="55"/>
-      <c r="B18" s="55"/>
-      <c r="C18" s="56"/>
-      <c r="D18" s="56"/>
-      <c r="E18" s="49"/>
-      <c r="F18" s="49"/>
-      <c r="G18" s="56"/>
-      <c r="H18" s="57"/>
-      <c r="I18" s="57"/>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A18" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No rutinario</t>
+        </is>
+      </c>
+      <c r="B18" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Arranque de la estación al inicio de turno</t>
+        </is>
+      </c>
+      <c r="C18" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paso 2 de 2: verifica luces indicadoras/status y realiza un ciclo de prueba si la estación lo requiere, confirmando que el área esté despejada</t>
+        </is>
+      </c>
+      <c r="D18" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mecanico</t>
+        </is>
+      </c>
+      <c r="E18" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partes móviles</t>
+        </is>
+      </c>
+      <c r="F18" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Atrapamiento</t>
+        </is>
+      </c>
+      <c r="G18" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control</t>
+        </is>
+      </c>
+      <c r="H18" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I18" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
       <c r="J18" s="51">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K18" s="107"/>
-      <c r="L18" s="58"/>
-      <c r="M18" s="58"/>
-      <c r="N18" s="57"/>
-      <c r="O18" s="49"/>
+      <c r="K18" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resguardos mecánicos</t>
+        </is>
+      </c>
+      <c r="L18" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
+        </is>
+      </c>
+      <c r="M18" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16-AT40-3318-00008
+16-AT40-3318-00009
+16-AT40-3318-00010
+16-AT40-3318-00011
+16-AT40-3318-00021
+16-AT40-3318-00024
+16-AT40-3318-00025
+(Front Assy Moose: numero de AV pendiente de confirmar, ilegible en la imagen enviada)</t>
+        </is>
+      </c>
+      <c r="N18" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O18" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
       <c r="P18" s="61">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -7318,25 +7621,88 @@
       <c r="R18" s="57"/>
       <c r="S18" s="57"/>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A19" s="55"/>
-      <c r="B19" s="55"/>
-      <c r="C19" s="56"/>
-      <c r="D19" s="56"/>
-      <c r="E19" s="49"/>
-      <c r="F19" s="49"/>
-      <c r="G19" s="56"/>
-      <c r="H19" s="57"/>
-      <c r="I19" s="57"/>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A19" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Emergencia </t>
+        </is>
+      </c>
+      <c r="B19" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Activación del botón de paro de emergencia ante una condición insegura</t>
+        </is>
+      </c>
+      <c r="C19" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El operador presiona el botón de paro de emergencia al detectar una condición insegura (atasco, ruido anormal, riesgo a persona) y notifica a su supervisor/mantenimiento</t>
+        </is>
+      </c>
+      <c r="D19" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mecanico</t>
+        </is>
+      </c>
+      <c r="E19" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partes móviles</t>
+        </is>
+      </c>
+      <c r="F19" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Atrapamiento</t>
+        </is>
+      </c>
+      <c r="G19" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control</t>
+        </is>
+      </c>
+      <c r="H19" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I19" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
       <c r="J19" s="51">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K19" s="107"/>
-      <c r="L19" s="58"/>
-      <c r="M19" s="58"/>
-      <c r="N19" s="57"/>
-      <c r="O19" s="49"/>
+      <c r="K19" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sensores</t>
+        </is>
+      </c>
+      <c r="L19" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
+        </is>
+      </c>
+      <c r="M19" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16-AT40-3318-00008
+16-AT40-3318-00009
+16-AT40-3318-00010
+16-AT40-3318-00011
+16-AT40-3318-00021
+16-AT40-3318-00024
+16-AT40-3318-00025
+(Front Assy Moose: numero de AV pendiente de confirmar, ilegible en la imagen enviada)</t>
+        </is>
+      </c>
+      <c r="N19" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O19" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
       <c r="P19" s="61">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -7348,25 +7714,88 @@
       <c r="R19" s="57"/>
       <c r="S19" s="57"/>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A20" s="55"/>
-      <c r="B20" s="55"/>
-      <c r="C20" s="56"/>
-      <c r="D20" s="56"/>
-      <c r="E20" s="49"/>
-      <c r="F20" s="49"/>
-      <c r="G20" s="56"/>
-      <c r="H20" s="57"/>
-      <c r="I20" s="57"/>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A20" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Emergencia </t>
+        </is>
+      </c>
+      <c r="B20" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reinicio del equipo después de un paro de emergencia</t>
+        </is>
+      </c>
+      <c r="C20" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Personal autorizado identifica y corrige la causa del paro, verifica que el área esté despejada antes de liberar el botón de paro y reiniciar el ciclo</t>
+        </is>
+      </c>
+      <c r="D20" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mecanico</t>
+        </is>
+      </c>
+      <c r="E20" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partes móviles</t>
+        </is>
+      </c>
+      <c r="F20" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Atrapamiento</t>
+        </is>
+      </c>
+      <c r="G20" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control</t>
+        </is>
+      </c>
+      <c r="H20" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="I20" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
       <c r="J20" s="51">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K20" s="107"/>
-      <c r="L20" s="58"/>
-      <c r="M20" s="58"/>
-      <c r="N20" s="57"/>
-      <c r="O20" s="49"/>
+      <c r="K20" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOTO</t>
+        </is>
+      </c>
+      <c r="L20" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
+        </is>
+      </c>
+      <c r="M20" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16-AT40-3318-00008
+16-AT40-3318-00009
+16-AT40-3318-00010
+16-AT40-3318-00011
+16-AT40-3318-00021
+16-AT40-3318-00024
+16-AT40-3318-00025
+(Front Assy Moose: numero de AV pendiente de confirmar, ilegible en la imagen enviada)</t>
+        </is>
+      </c>
+      <c r="N20" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O20" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
       <c r="P20" s="61">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -7378,25 +7807,88 @@
       <c r="R20" s="57"/>
       <c r="S20" s="57"/>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A21" s="55"/>
-      <c r="B21" s="55"/>
-      <c r="C21" s="56"/>
-      <c r="D21" s="56"/>
-      <c r="E21" s="49"/>
-      <c r="F21" s="49"/>
-      <c r="G21" s="56"/>
-      <c r="H21" s="57"/>
-      <c r="I21" s="57"/>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A21" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No rutinario</t>
+        </is>
+      </c>
+      <c r="B21" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mantenimiento correctivo eléctrico</t>
+        </is>
+      </c>
+      <c r="C21" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paso 1 de 4: bloquea y etiqueta (LOTO) el switch general de desconexión antes de intervenir</t>
+        </is>
+      </c>
+      <c r="D21" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mecanico</t>
+        </is>
+      </c>
+      <c r="E21" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partes móviles</t>
+        </is>
+      </c>
+      <c r="F21" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Atrapamiento</t>
+        </is>
+      </c>
+      <c r="G21" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control</t>
+        </is>
+      </c>
+      <c r="H21" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="I21" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
       <c r="J21" s="51">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K21" s="107"/>
-      <c r="L21" s="58"/>
-      <c r="M21" s="58"/>
-      <c r="N21" s="57"/>
-      <c r="O21" s="49"/>
+      <c r="K21" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOTO</t>
+        </is>
+      </c>
+      <c r="L21" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7. Adicional para intervención eléctrica: guantes dieléctricos (clase según voltaje) y calzado aislante.</t>
+        </is>
+      </c>
+      <c r="M21" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16-AT40-3318-00008
+16-AT40-3318-00009
+16-AT40-3318-00010
+16-AT40-3318-00011
+16-AT40-3318-00021
+16-AT40-3318-00024
+16-AT40-3318-00025
+(Front Assy Moose: numero de AV pendiente de confirmar, ilegible en la imagen enviada)</t>
+        </is>
+      </c>
+      <c r="N21" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O21" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
       <c r="P21" s="61">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -7408,25 +7900,88 @@
       <c r="R21" s="57"/>
       <c r="S21" s="57"/>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A22" s="55"/>
-      <c r="B22" s="55"/>
-      <c r="C22" s="56"/>
-      <c r="D22" s="56"/>
-      <c r="E22" s="49"/>
-      <c r="F22" s="49"/>
-      <c r="G22" s="56"/>
-      <c r="H22" s="57"/>
-      <c r="I22" s="57"/>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A22" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No rutinario</t>
+        </is>
+      </c>
+      <c r="B22" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mantenimiento correctivo eléctrico</t>
+        </is>
+      </c>
+      <c r="C22" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paso 2 de 4: abre el panel/gabinete eléctrico de la estación para diagnóstico</t>
+        </is>
+      </c>
+      <c r="D22" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eléctrico</t>
+        </is>
+      </c>
+      <c r="E22" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Conductores energizados</t>
+        </is>
+      </c>
+      <c r="F22" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Electrocución</t>
+        </is>
+      </c>
+      <c r="G22" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control</t>
+        </is>
+      </c>
+      <c r="H22" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="I22" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
       <c r="J22" s="51">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K22" s="107"/>
-      <c r="L22" s="58"/>
-      <c r="M22" s="58"/>
-      <c r="N22" s="57"/>
-      <c r="O22" s="49"/>
+      <c r="K22" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOTO</t>
+        </is>
+      </c>
+      <c r="L22" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7. Adicional para intervención eléctrica: guantes dieléctricos (clase según voltaje) y calzado aislante.</t>
+        </is>
+      </c>
+      <c r="M22" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16-AT40-3318-00008
+16-AT40-3318-00009
+16-AT40-3318-00010
+16-AT40-3318-00011
+16-AT40-3318-00021
+16-AT40-3318-00024
+16-AT40-3318-00025
+(Front Assy Moose: numero de AV pendiente de confirmar, ilegible en la imagen enviada)</t>
+        </is>
+      </c>
+      <c r="N22" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O22" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
       <c r="P22" s="61">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -7438,25 +7993,88 @@
       <c r="R22" s="57"/>
       <c r="S22" s="57"/>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A23" s="55"/>
-      <c r="B23" s="55"/>
-      <c r="C23" s="56"/>
-      <c r="D23" s="56"/>
-      <c r="E23" s="49"/>
-      <c r="F23" s="49"/>
-      <c r="G23" s="56"/>
-      <c r="H23" s="57"/>
-      <c r="I23" s="57"/>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A23" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No rutinario</t>
+        </is>
+      </c>
+      <c r="B23" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mantenimiento correctivo eléctrico</t>
+        </is>
+      </c>
+      <c r="C23" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paso 3 de 4: repara o reemplaza el componente dañado y cierra el gabinete</t>
+        </is>
+      </c>
+      <c r="D23" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eléctrico</t>
+        </is>
+      </c>
+      <c r="E23" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Conductores energizados</t>
+        </is>
+      </c>
+      <c r="F23" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Electrocución</t>
+        </is>
+      </c>
+      <c r="G23" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control</t>
+        </is>
+      </c>
+      <c r="H23" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="I23" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
       <c r="J23" s="51">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K23" s="107"/>
-      <c r="L23" s="58"/>
-      <c r="M23" s="58"/>
-      <c r="N23" s="57"/>
-      <c r="O23" s="49"/>
+      <c r="K23" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOTO</t>
+        </is>
+      </c>
+      <c r="L23" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7. Adicional para intervención eléctrica: guantes dieléctricos (clase según voltaje) y calzado aislante.</t>
+        </is>
+      </c>
+      <c r="M23" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16-AT40-3318-00008
+16-AT40-3318-00009
+16-AT40-3318-00010
+16-AT40-3318-00011
+16-AT40-3318-00021
+16-AT40-3318-00024
+16-AT40-3318-00025
+(Front Assy Moose: numero de AV pendiente de confirmar, ilegible en la imagen enviada)</t>
+        </is>
+      </c>
+      <c r="N23" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O23" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
       <c r="P23" s="61">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -7468,25 +8086,88 @@
       <c r="R23" s="57"/>
       <c r="S23" s="57"/>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A24" s="55"/>
-      <c r="B24" s="55"/>
-      <c r="C24" s="56"/>
-      <c r="D24" s="56"/>
-      <c r="E24" s="49"/>
-      <c r="F24" s="49"/>
-      <c r="G24" s="56"/>
-      <c r="H24" s="57"/>
-      <c r="I24" s="57"/>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A24" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No rutinario</t>
+        </is>
+      </c>
+      <c r="B24" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mantenimiento correctivo eléctrico</t>
+        </is>
+      </c>
+      <c r="C24" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paso 4 de 4: retira el candado/tarjeta de bloqueo (LOTO) y realiza una prueba funcional del equipo</t>
+        </is>
+      </c>
+      <c r="D24" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mecanico</t>
+        </is>
+      </c>
+      <c r="E24" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partes móviles</t>
+        </is>
+      </c>
+      <c r="F24" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Atrapamiento</t>
+        </is>
+      </c>
+      <c r="G24" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control</t>
+        </is>
+      </c>
+      <c r="H24" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="I24" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
       <c r="J24" s="51">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K24" s="107"/>
-      <c r="L24" s="58"/>
-      <c r="M24" s="58"/>
-      <c r="N24" s="57"/>
-      <c r="O24" s="49"/>
+      <c r="K24" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOTO</t>
+        </is>
+      </c>
+      <c r="L24" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
+        </is>
+      </c>
+      <c r="M24" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16-AT40-3318-00008
+16-AT40-3318-00009
+16-AT40-3318-00010
+16-AT40-3318-00011
+16-AT40-3318-00021
+16-AT40-3318-00024
+16-AT40-3318-00025
+(Front Assy Moose: numero de AV pendiente de confirmar, ilegible en la imagen enviada)</t>
+        </is>
+      </c>
+      <c r="N24" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O24" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
       <c r="P24" s="61">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -7498,25 +8179,88 @@
       <c r="R24" s="57"/>
       <c r="S24" s="57"/>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A25" s="55"/>
-      <c r="B25" s="55"/>
-      <c r="C25" s="56"/>
-      <c r="D25" s="56"/>
-      <c r="E25" s="49"/>
-      <c r="F25" s="49"/>
-      <c r="G25" s="56"/>
-      <c r="H25" s="57"/>
-      <c r="I25" s="57"/>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A25" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No rutinario</t>
+        </is>
+      </c>
+      <c r="B25" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mantenimiento neumático (en las estaciones con pistones de fixtura)</t>
+        </is>
+      </c>
+      <c r="C25" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paso 1 de 2: despresuriza la línea y coloca el clip de bloqueo neumático tipo C portátil (candado y tarjeta) en el acople rápido</t>
+        </is>
+      </c>
+      <c r="D25" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mecanico</t>
+        </is>
+      </c>
+      <c r="E25" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sistema de presión</t>
+        </is>
+      </c>
+      <c r="F25" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Laceraciones</t>
+        </is>
+      </c>
+      <c r="G25" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control</t>
+        </is>
+      </c>
+      <c r="H25" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="I25" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
       <c r="J25" s="51">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K25" s="107"/>
-      <c r="L25" s="58"/>
-      <c r="M25" s="58"/>
-      <c r="N25" s="57"/>
-      <c r="O25" s="49"/>
+      <c r="K25" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Válvulas de alivio</t>
+        </is>
+      </c>
+      <c r="L25" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7. Adicional: usar clip de bloqueo neumático tipo C (candado + tarjeta) en el acople rápido de aire en las estaciones sin válvula LOTO integrada.</t>
+        </is>
+      </c>
+      <c r="M25" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16-AT40-3318-00008
+16-AT40-3318-00009
+16-AT40-3318-00010
+16-AT40-3318-00011
+16-AT40-3318-00021
+16-AT40-3318-00024
+16-AT40-3318-00025
+(Front Assy Moose: numero de AV pendiente de confirmar, ilegible en la imagen enviada)</t>
+        </is>
+      </c>
+      <c r="N25" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O25" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
       <c r="P25" s="61">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -7528,25 +8272,88 @@
       <c r="R25" s="57"/>
       <c r="S25" s="57"/>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A26" s="55"/>
-      <c r="B26" s="55"/>
-      <c r="C26" s="56"/>
-      <c r="D26" s="56"/>
-      <c r="E26" s="49"/>
-      <c r="F26" s="49"/>
-      <c r="G26" s="56"/>
-      <c r="H26" s="57"/>
-      <c r="I26" s="57"/>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A26" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No rutinario</t>
+        </is>
+      </c>
+      <c r="B26" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mantenimiento neumático (en las estaciones con pistones de fixtura)</t>
+        </is>
+      </c>
+      <c r="C26" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paso 2 de 2: interviene cilindros o mangueras y verifica energía cero antes de retirar el bloqueo</t>
+        </is>
+      </c>
+      <c r="D26" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mecanico</t>
+        </is>
+      </c>
+      <c r="E26" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sistema de presión</t>
+        </is>
+      </c>
+      <c r="F26" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Laceraciones</t>
+        </is>
+      </c>
+      <c r="G26" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control</t>
+        </is>
+      </c>
+      <c r="H26" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="I26" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
       <c r="J26" s="51">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K26" s="107"/>
-      <c r="L26" s="58"/>
-      <c r="M26" s="58"/>
-      <c r="N26" s="57"/>
-      <c r="O26" s="49"/>
+      <c r="K26" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Válvulas de alivio</t>
+        </is>
+      </c>
+      <c r="L26" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7. Adicional: usar clip de bloqueo neumático tipo C (candado + tarjeta) en el acople rápido de aire en las estaciones sin válvula LOTO integrada.</t>
+        </is>
+      </c>
+      <c r="M26" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16-AT40-3318-00008
+16-AT40-3318-00009
+16-AT40-3318-00010
+16-AT40-3318-00011
+16-AT40-3318-00021
+16-AT40-3318-00024
+16-AT40-3318-00025
+(Front Assy Moose: numero de AV pendiente de confirmar, ilegible en la imagen enviada)</t>
+        </is>
+      </c>
+      <c r="N26" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O26" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
       <c r="P26" s="61">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -7558,25 +8365,88 @@
       <c r="R26" s="57"/>
       <c r="S26" s="57"/>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A27" s="55"/>
-      <c r="B27" s="55"/>
-      <c r="C27" s="56"/>
-      <c r="D27" s="56"/>
-      <c r="E27" s="49"/>
-      <c r="F27" s="49"/>
-      <c r="G27" s="56"/>
-      <c r="H27" s="57"/>
-      <c r="I27" s="57"/>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A27" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No rutinario</t>
+        </is>
+      </c>
+      <c r="B27" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mantenimiento al atornillador (bloqueo y etiquetado)</t>
+        </is>
+      </c>
+      <c r="C27" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El personal de mantenimiento bloquea el switch general de desconexión antes de intervenir el atornillador o la fixtura</t>
+        </is>
+      </c>
+      <c r="D27" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mecanico</t>
+        </is>
+      </c>
+      <c r="E27" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partes móviles</t>
+        </is>
+      </c>
+      <c r="F27" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Atrapamiento</t>
+        </is>
+      </c>
+      <c r="G27" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control</t>
+        </is>
+      </c>
+      <c r="H27" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I27" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
       <c r="J27" s="51">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K27" s="107"/>
-      <c r="L27" s="58"/>
-      <c r="M27" s="58"/>
-      <c r="N27" s="57"/>
-      <c r="O27" s="49"/>
+      <c r="K27" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOTO</t>
+        </is>
+      </c>
+      <c r="L27" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
+        </is>
+      </c>
+      <c r="M27" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16-AT40-3318-00008
+16-AT40-3318-00009
+16-AT40-3318-00010
+16-AT40-3318-00011
+16-AT40-3318-00021
+16-AT40-3318-00024
+16-AT40-3318-00025
+(Front Assy Moose: numero de AV pendiente de confirmar, ilegible en la imagen enviada)</t>
+        </is>
+      </c>
+      <c r="N27" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O27" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
       <c r="P27" s="61">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -7588,18 +8458,36 @@
       <c r="R27" s="57"/>
       <c r="S27" s="57"/>
     </row>
-    <row r="28" spans="1:19" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:19" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="K28" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="29" spans="1:19" ht="39.9" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="1:19" ht="39.9" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="1:19" ht="39.9" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:19" ht="39.9" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="33" ht="39" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:19" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="30" spans="1:19" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="31" spans="1:19" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="32" spans="1:19" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="33" ht="39" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="34">
+    <mergeCell ref="S6:S7"/>
+    <mergeCell ref="P5:S5"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P4:S4"/>
+    <mergeCell ref="H3:K3"/>
+    <mergeCell ref="N6:N7"/>
+    <mergeCell ref="P2:S2"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="P3:S3"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="H5:K5"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="H4:K4"/>
+    <mergeCell ref="G6:G7"/>
     <mergeCell ref="E1:G1"/>
     <mergeCell ref="K6:K7"/>
     <mergeCell ref="A5:D5"/>
@@ -7616,62 +8504,44 @@
     <mergeCell ref="R6:R7"/>
     <mergeCell ref="N4:O4"/>
     <mergeCell ref="E3:G4"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="H5:K5"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="H4:K4"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="S6:S7"/>
-    <mergeCell ref="P5:S5"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P4:S4"/>
-    <mergeCell ref="H3:K3"/>
-    <mergeCell ref="N6:N7"/>
-    <mergeCell ref="P2:S2"/>
-    <mergeCell ref="N5:O5"/>
-    <mergeCell ref="P3:S3"/>
-    <mergeCell ref="N3:O3"/>
   </mergeCells>
   <conditionalFormatting sqref="J8:J27 P8:P27">
-    <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="2" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J8:J27">
-    <cfRule type="cellIs" dxfId="7" priority="7" operator="between">
+    <cfRule type="cellIs" dxfId="18" priority="7" operator="between">
       <formula>17</formula>
       <formula>25</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="8" operator="between">
+    <cfRule type="cellIs" dxfId="17" priority="8" operator="between">
       <formula>10</formula>
       <formula>16</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="9" operator="between">
+    <cfRule type="cellIs" dxfId="16" priority="9" operator="between">
       <formula>4</formula>
       <formula>9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="10" operator="between">
+    <cfRule type="cellIs" dxfId="15" priority="10" operator="between">
       <formula>1</formula>
       <formula>3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P8:P27">
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="between">
+    <cfRule type="cellIs" dxfId="14" priority="3" operator="between">
       <formula>17</formula>
       <formula>25</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="between">
+    <cfRule type="cellIs" dxfId="13" priority="4" operator="between">
       <formula>10</formula>
       <formula>16.9999999999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="5" operator="between">
+    <cfRule type="cellIs" dxfId="12" priority="5" operator="between">
       <formula>4</formula>
       <formula>9.99999999999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="6" operator="between">
+    <cfRule type="cellIs" dxfId="11" priority="6" operator="between">
       <formula>0</formula>
       <formula>3.99999999999999</formula>
     </cfRule>
@@ -7756,149 +8626,149 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:A29"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="18" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="18" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="18" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="18" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="18" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="9" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="18" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="18" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="11" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="18" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="12" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="18" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="13" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="14" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="18" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="15" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="16" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="18" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="18" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="18" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="19" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="18" t="s">
         <v>496</v>
       </c>
     </row>
-    <row r="20" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="18" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="21" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="18" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="22" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="18" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="23" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="18" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="24" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="18" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="25" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="18" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="26" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="18" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="27" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="18" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="28" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="18" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="29" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="18" t="s">
         <v>506</v>
       </c>
@@ -7912,12 +8782,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:L50"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="165" t="s">
         <v>507</v>
       </c>
@@ -7933,16 +8803,16 @@
       <c r="K1" s="156"/>
       <c r="L1" s="156"/>
     </row>
-    <row r="2" spans="1:12" ht="12.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="162" t="s">
         <v>508</v>
       </c>
-      <c r="B2" s="125"/>
-      <c r="C2" s="125"/>
-      <c r="D2" s="125"/>
-      <c r="E2" s="125"/>
-    </row>
-    <row r="3" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="136"/>
+      <c r="C2" s="136"/>
+      <c r="D2" s="136"/>
+      <c r="E2" s="136"/>
+    </row>
+    <row r="3" spans="1:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>509</v>
       </c>
@@ -7953,7 +8823,7 @@
       <c r="D3" s="9"/>
       <c r="E3" s="10"/>
     </row>
-    <row r="4" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="4" t="s">
@@ -7962,7 +8832,7 @@
       <c r="D4" s="9"/>
       <c r="E4" s="10"/>
     </row>
-    <row r="5" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="4" t="s">
@@ -7971,7 +8841,7 @@
       <c r="D5" s="9"/>
       <c r="E5" s="10"/>
     </row>
-    <row r="6" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
       <c r="C6" s="4" t="s">
@@ -7980,7 +8850,7 @@
       <c r="D6" s="9"/>
       <c r="E6" s="10"/>
     </row>
-    <row r="7" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>514</v>
       </c>
@@ -7990,7 +8860,7 @@
       </c>
       <c r="D7" s="9"/>
     </row>
-    <row r="8" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="4" t="s">
@@ -7999,7 +8869,7 @@
       <c r="D8" s="9"/>
       <c r="E8" s="10"/>
     </row>
-    <row r="9" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>492</v>
       </c>
@@ -8009,7 +8879,7 @@
       </c>
       <c r="D9" s="9"/>
     </row>
-    <row r="10" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="C10" s="4" t="s">
@@ -8018,7 +8888,7 @@
       <c r="D10" s="9"/>
       <c r="E10" s="10"/>
     </row>
-    <row r="11" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>519</v>
       </c>
@@ -8028,7 +8898,7 @@
       </c>
       <c r="D11" s="9"/>
     </row>
-    <row r="12" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="4" t="s">
@@ -8037,7 +8907,7 @@
       <c r="D12" s="9"/>
       <c r="E12" s="10"/>
     </row>
-    <row r="13" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="163" t="s">
         <v>522</v>
       </c>
@@ -8048,7 +8918,7 @@
       <c r="D13" s="11"/>
       <c r="E13" s="10"/>
     </row>
-    <row r="14" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="161"/>
       <c r="B14" s="5"/>
       <c r="C14" s="4" t="s">
@@ -8057,7 +8927,7 @@
       <c r="D14" s="9"/>
       <c r="E14" s="10"/>
     </row>
-    <row r="15" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="5"/>
       <c r="B15" s="5"/>
       <c r="C15" s="4" t="s">
@@ -8066,7 +8936,7 @@
       <c r="D15" s="9"/>
       <c r="E15" s="10"/>
     </row>
-    <row r="16" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="5"/>
       <c r="B16" s="5"/>
       <c r="C16" s="4" t="s">
@@ -8075,7 +8945,7 @@
       <c r="D16" s="9"/>
       <c r="E16" s="10"/>
     </row>
-    <row r="17" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>527</v>
       </c>
@@ -8085,7 +8955,7 @@
       </c>
       <c r="D17" s="9"/>
     </row>
-    <row r="18" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
       <c r="C18" s="4" t="s">
@@ -8094,7 +8964,7 @@
       <c r="D18" s="9"/>
       <c r="E18" s="10"/>
     </row>
-    <row r="19" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
       <c r="C19" s="4" t="s">
@@ -8103,7 +8973,7 @@
       <c r="D19" s="9"/>
       <c r="E19" s="10"/>
     </row>
-    <row r="20" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>531</v>
       </c>
@@ -8113,7 +8983,7 @@
       </c>
       <c r="D20" s="9"/>
     </row>
-    <row r="21" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3"/>
       <c r="B21" s="3"/>
       <c r="C21" s="4" t="s">
@@ -8122,7 +8992,7 @@
       <c r="D21" s="9"/>
       <c r="E21" s="10"/>
     </row>
-    <row r="22" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
       <c r="C22" s="4" t="s">
@@ -8131,7 +9001,7 @@
       <c r="D22" s="9"/>
       <c r="E22" s="10"/>
     </row>
-    <row r="23" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>535</v>
       </c>
@@ -8141,7 +9011,7 @@
       </c>
       <c r="D23" s="9"/>
     </row>
-    <row r="24" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
       <c r="C24" s="4" t="s">
@@ -8150,7 +9020,7 @@
       <c r="D24" s="9"/>
       <c r="E24" s="10"/>
     </row>
-    <row r="25" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
       <c r="C25" s="4" t="s">
@@ -8158,7 +9028,7 @@
       </c>
       <c r="D25" s="9"/>
     </row>
-    <row r="26" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3"/>
       <c r="B26" s="3"/>
       <c r="C26" s="4" t="s">
@@ -8167,7 +9037,7 @@
       <c r="D26" s="9"/>
       <c r="E26" s="10"/>
     </row>
-    <row r="27" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3"/>
       <c r="B27" s="3"/>
       <c r="C27" s="4" t="s">
@@ -8175,7 +9045,7 @@
       </c>
       <c r="D27" s="9"/>
     </row>
-    <row r="28" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
       <c r="C28" s="4" t="s">
@@ -8184,7 +9054,7 @@
       <c r="D28" s="9"/>
       <c r="E28" s="10"/>
     </row>
-    <row r="29" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3"/>
       <c r="B29" s="3"/>
       <c r="C29" s="4" t="s">
@@ -8193,7 +9063,7 @@
       <c r="D29" s="9"/>
       <c r="E29" s="10"/>
     </row>
-    <row r="30" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="8" t="s">
         <v>543</v>
       </c>
@@ -8203,7 +9073,7 @@
       </c>
       <c r="D30" s="9"/>
     </row>
-    <row r="31" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="8"/>
       <c r="B31" s="5"/>
       <c r="C31" s="4" t="s">
@@ -8212,7 +9082,7 @@
       <c r="D31" s="9"/>
       <c r="E31" s="10"/>
     </row>
-    <row r="32" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="8"/>
       <c r="B32" s="5"/>
       <c r="C32" s="4" t="s">
@@ -8220,7 +9090,7 @@
       </c>
       <c r="D32" s="9"/>
     </row>
-    <row r="33" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="8"/>
       <c r="B33" s="5"/>
       <c r="C33" s="4" t="s">
@@ -8229,7 +9099,7 @@
       <c r="D33" s="9"/>
       <c r="E33" s="10"/>
     </row>
-    <row r="34" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="8" t="s">
         <v>548</v>
       </c>
@@ -8239,7 +9109,7 @@
       </c>
       <c r="D34" s="9"/>
     </row>
-    <row r="35" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="8"/>
       <c r="B35" s="5"/>
       <c r="C35" s="4" t="s">
@@ -8248,7 +9118,7 @@
       <c r="D35" s="9"/>
       <c r="E35" s="10"/>
     </row>
-    <row r="36" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="8"/>
       <c r="B36" s="5"/>
       <c r="C36" s="4" t="s">
@@ -8256,7 +9126,7 @@
       </c>
       <c r="D36" s="9"/>
     </row>
-    <row r="37" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="8"/>
       <c r="B37" s="5"/>
       <c r="C37" s="4" t="s">
@@ -8265,7 +9135,7 @@
       <c r="D37" s="9"/>
       <c r="E37" s="10"/>
     </row>
-    <row r="38" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="5"/>
       <c r="B38" s="5"/>
       <c r="C38" s="4" t="s">
@@ -8273,7 +9143,7 @@
       </c>
       <c r="D38" s="9"/>
     </row>
-    <row r="39" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="5"/>
       <c r="B39" s="5"/>
       <c r="C39" s="4" t="s">
@@ -8282,7 +9152,7 @@
       <c r="D39" s="9"/>
       <c r="E39" s="10"/>
     </row>
-    <row r="40" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>555</v>
       </c>
@@ -8291,7 +9161,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3"/>
       <c r="B41" s="3"/>
       <c r="C41" s="7" t="s">
@@ -8299,7 +9169,7 @@
       </c>
       <c r="E41" s="12"/>
     </row>
-    <row r="42" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3"/>
       <c r="B42" s="3"/>
       <c r="C42" s="7" t="s">
@@ -8307,7 +9177,7 @@
       </c>
       <c r="E42" s="12"/>
     </row>
-    <row r="43" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3"/>
       <c r="B43" s="3"/>
       <c r="C43" s="7" t="s">
@@ -8316,7 +9186,7 @@
       <c r="D43" s="12"/>
       <c r="E43" s="12"/>
     </row>
-    <row r="44" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3"/>
       <c r="B44" s="3"/>
       <c r="C44" s="7" t="s">
@@ -8325,7 +9195,7 @@
       <c r="D44" s="12"/>
       <c r="E44" s="12"/>
     </row>
-    <row r="45" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3"/>
       <c r="B45" s="3"/>
       <c r="C45" s="7" t="s">
@@ -8334,7 +9204,7 @@
       <c r="D45" s="12"/>
       <c r="E45" s="12"/>
     </row>
-    <row r="46" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3"/>
       <c r="B46" s="3"/>
       <c r="C46" s="7" t="s">
@@ -8343,23 +9213,23 @@
       <c r="D46" s="12"/>
       <c r="E46" s="12"/>
     </row>
-    <row r="47" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>563</v>
       </c>
       <c r="B47" s="164" t="s">
         <v>564</v>
       </c>
-      <c r="C47" s="121"/>
-      <c r="D47" s="121"/>
-      <c r="E47" s="122"/>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C47" s="119"/>
+      <c r="D47" s="119"/>
+      <c r="E47" s="120"/>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>565</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>566</v>
       </c>
@@ -8380,19 +9250,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:I8"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="44.33203125" customWidth="1"/>
-    <col min="3" max="3" width="9.33203125" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="44.28515625" customWidth="1"/>
+    <col min="3" max="3" width="9.28515625" customWidth="1"/>
+    <col min="6" max="6" width="11.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C1" s="2" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>568</v>
       </c>
@@ -8403,7 +9273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>569</v>
       </c>
@@ -8414,7 +9284,7 @@
         <v>-0.1</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>570</v>
       </c>
@@ -8425,7 +9295,7 @@
         <v>-0.1</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>571</v>
       </c>
@@ -8436,7 +9306,7 @@
         <v>-0.1</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="12.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>572</v>
       </c>
@@ -8453,7 +9323,7 @@
       <c r="H6" s="14"/>
       <c r="I6" s="14"/>
     </row>
-    <row r="7" spans="1:9" ht="12.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>573</v>
       </c>
@@ -8467,7 +9337,7 @@
       <c r="E7" s="14"/>
       <c r="F7" s="14"/>
     </row>
-    <row r="8" spans="1:9" ht="12.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>574</v>
       </c>
@@ -8490,14 +9360,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:3" ht="12.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C1" s="1" t="s">
         <v>575</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -8505,7 +9375,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -8513,7 +9383,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -8521,7 +9391,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -8529,7 +9399,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -8545,20 +9415,20 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:I2009"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>381</v>
       </c>
@@ -8587,7 +9457,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>382</v>
       </c>
@@ -8616,7 +9486,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>385</v>
       </c>
@@ -8645,7 +9515,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>388</v>
       </c>
@@ -8674,7 +9544,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>391</v>
       </c>
@@ -8703,7 +9573,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>394</v>
       </c>
@@ -8726,7 +9596,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
         <v>418</v>
       </c>
@@ -8743,7 +9613,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
         <v>421</v>
       </c>
@@ -8760,7 +9630,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
         <v>407</v>
       </c>
@@ -8774,7 +9644,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
         <v>410</v>
       </c>
@@ -8788,7 +9658,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="E11" t="s">
         <v>290</v>
       </c>
@@ -8799,7 +9669,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="E12" t="s">
         <v>293</v>
       </c>
@@ -8807,7 +9677,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="E13" t="s">
         <v>295</v>
       </c>
@@ -8815,7 +9685,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="E14" t="s">
         <v>298</v>
       </c>
@@ -8823,7 +9693,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="E15" t="s">
         <v>301</v>
       </c>
@@ -8831,7 +9701,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="E16" t="s">
         <v>305</v>
       </c>
@@ -8839,7 +9709,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="17" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E17" t="s">
         <v>308</v>
       </c>
@@ -8847,7 +9717,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="18" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E18" t="s">
         <v>311</v>
       </c>
@@ -8855,7 +9725,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="19" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E19" t="s">
         <v>313</v>
       </c>
@@ -8863,92 +9733,92 @@
         <v>259</v>
       </c>
     </row>
-    <row r="20" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E20" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="21" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E21" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="22" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E22" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="23" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E23" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="24" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E24" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="25" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E25" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="26" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E26" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="27" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E27" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="2000" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2000" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2000" t="s">
         <v>581</v>
       </c>
     </row>
-    <row r="2001" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2001" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2001" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="2002" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2002" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2002" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="2003" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2003" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2003" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="2004" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2004" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2004" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="2005" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2005" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2005" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="2006" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2006" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2006" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="2007" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2007" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2007" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="2008" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2008" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2008" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="2009" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2009" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2009" t="s">
         <v>52</v>
       </c>
@@ -8961,9 +9831,9 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:CM5"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:91" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:91" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>219</v>
       </c>
@@ -9238,7 +10108,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="2" spans="1:91" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:91" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>582</v>
       </c>
@@ -9513,7 +10383,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="3" spans="1:91" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:91" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>655</v>
       </c>
@@ -9770,7 +10640,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="4" spans="1:91" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:91" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>725</v>
       </c>
@@ -9874,7 +10744,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="5" spans="1:91" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:91" x14ac:dyDescent="0.2">
       <c r="H5" t="s">
         <v>752</v>
       </c>
@@ -9905,9 +10775,9 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:B92"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>14</v>
       </c>
@@ -9915,7 +10785,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>219</v>
       </c>
@@ -9923,7 +10793,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>319</v>
       </c>
@@ -9931,7 +10801,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>410</v>
       </c>
@@ -9939,7 +10809,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>336</v>
       </c>
@@ -9947,7 +10817,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>458</v>
       </c>
@@ -9955,7 +10825,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>256</v>
       </c>
@@ -9963,7 +10833,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>391</v>
       </c>
@@ -9971,7 +10841,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>206</v>
       </c>
@@ -9979,7 +10849,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>167</v>
       </c>
@@ -9987,7 +10857,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>418</v>
       </c>
@@ -9995,7 +10865,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>447</v>
       </c>
@@ -10003,7 +10873,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>216</v>
       </c>
@@ -10011,7 +10881,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>201</v>
       </c>
@@ -10019,7 +10889,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>287</v>
       </c>
@@ -10027,7 +10897,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>298</v>
       </c>
@@ -10035,7 +10905,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>332</v>
       </c>
@@ -10043,7 +10913,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>363</v>
       </c>
@@ -10051,7 +10921,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>225</v>
       </c>
@@ -10059,7 +10929,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>205</v>
       </c>
@@ -10067,7 +10937,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>209</v>
       </c>
@@ -10075,7 +10945,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>265</v>
       </c>
@@ -10083,7 +10953,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>262</v>
       </c>
@@ -10091,7 +10961,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>326</v>
       </c>
@@ -10099,7 +10969,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>385</v>
       </c>
@@ -10107,7 +10977,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>360</v>
       </c>
@@ -10115,7 +10985,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>357</v>
       </c>
@@ -10123,7 +10993,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>394</v>
       </c>
@@ -10131,7 +11001,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>434</v>
       </c>
@@ -10139,7 +11009,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>343</v>
       </c>
@@ -10147,7 +11017,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>455</v>
       </c>
@@ -10155,7 +11025,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>401</v>
       </c>
@@ -10163,7 +11033,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>465</v>
       </c>
@@ -10171,7 +11041,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>283</v>
       </c>
@@ -10179,7 +11049,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>438</v>
       </c>
@@ -10187,7 +11057,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>222</v>
       </c>
@@ -10195,7 +11065,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>370</v>
       </c>
@@ -10203,7 +11073,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>372</v>
       </c>
@@ -10211,7 +11081,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>301</v>
       </c>
@@ -10219,7 +11089,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>339</v>
       </c>
@@ -10227,7 +11097,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>426</v>
       </c>
@@ -10235,7 +11105,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>311</v>
       </c>
@@ -10243,7 +11113,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>345</v>
       </c>
@@ -10251,7 +11121,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>295</v>
       </c>
@@ -10259,7 +11129,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>329</v>
       </c>
@@ -10267,7 +11137,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>436</v>
       </c>
@@ -10275,7 +11145,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>253</v>
       </c>
@@ -10283,7 +11153,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>440</v>
       </c>
@@ -10291,7 +11161,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>398</v>
       </c>
@@ -10299,7 +11169,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>228</v>
       </c>
@@ -10307,7 +11177,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>293</v>
       </c>
@@ -10315,7 +11185,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>428</v>
       </c>
@@ -10323,7 +11193,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>378</v>
       </c>
@@ -10331,7 +11201,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>407</v>
       </c>
@@ -10339,7 +11209,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>305</v>
       </c>
@@ -10347,7 +11217,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>281</v>
       </c>
@@ -10355,7 +11225,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>53</v>
       </c>
@@ -10363,7 +11233,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>404</v>
       </c>
@@ -10371,7 +11241,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>313</v>
       </c>
@@ -10379,7 +11249,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>271</v>
       </c>
@@ -10387,7 +11257,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>445</v>
       </c>
@@ -10395,7 +11265,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>422</v>
       </c>
@@ -10403,7 +11273,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>259</v>
       </c>
@@ -10411,7 +11281,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>347</v>
       </c>
@@ -10419,7 +11289,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>322</v>
       </c>
@@ -10427,7 +11297,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>290</v>
       </c>
@@ -10435,7 +11305,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>431</v>
       </c>
@@ -10443,7 +11313,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>413</v>
       </c>
@@ -10451,7 +11321,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>367</v>
       </c>
@@ -10459,7 +11329,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>382</v>
       </c>
@@ -10467,7 +11337,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>316</v>
       </c>
@@ -10475,7 +11345,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>242</v>
       </c>
@@ -10483,7 +11353,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>246</v>
       </c>
@@ -10491,7 +11361,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>268</v>
       </c>
@@ -10499,7 +11369,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>443</v>
       </c>
@@ -10507,7 +11377,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>451</v>
       </c>
@@ -10515,7 +11385,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>172</v>
       </c>
@@ -10523,7 +11393,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>353</v>
       </c>
@@ -10531,7 +11401,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>51</v>
       </c>
@@ -10539,7 +11409,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>52</v>
       </c>
@@ -10547,7 +11417,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>308</v>
       </c>
@@ -10555,7 +11425,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>249</v>
       </c>
@@ -10563,7 +11433,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>231</v>
       </c>
@@ -10571,7 +11441,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>416</v>
       </c>
@@ -10579,7 +11449,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>278</v>
       </c>
@@ -10587,7 +11457,7 @@
         <v>841</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>375</v>
       </c>
@@ -10595,7 +11465,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>421</v>
       </c>
@@ -10603,7 +11473,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>388</v>
       </c>
@@ -10611,7 +11481,7 @@
         <v>844</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>461</v>
       </c>
@@ -10619,7 +11489,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>274</v>
       </c>
@@ -10627,7 +11497,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>238</v>
       </c>
@@ -10635,7 +11505,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>350</v>
       </c>
@@ -10651,9 +11521,9 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:CJ5"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:88" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>219</v>
       </c>
@@ -10919,7 +11789,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="2" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:88" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>618</v>
       </c>
@@ -11185,7 +12055,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="3" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:88" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>864</v>
       </c>
@@ -11436,7 +12306,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="4" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:88" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>880</v>
       </c>
@@ -11669,7 +12539,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="5" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:88" x14ac:dyDescent="0.2">
       <c r="I5" t="s">
         <v>891</v>
       </c>
@@ -11742,9 +12612,9 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:B89"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>14</v>
       </c>
@@ -11752,7 +12622,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>219</v>
       </c>
@@ -11760,7 +12630,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>319</v>
       </c>
@@ -11768,7 +12638,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>410</v>
       </c>
@@ -11776,7 +12646,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>336</v>
       </c>
@@ -11784,7 +12654,7 @@
         <v>898</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>458</v>
       </c>
@@ -11792,7 +12662,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>256</v>
       </c>
@@ -11800,7 +12670,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>391</v>
       </c>
@@ -11808,7 +12678,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>206</v>
       </c>
@@ -11816,7 +12686,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>167</v>
       </c>
@@ -11824,7 +12694,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>418</v>
       </c>
@@ -11832,7 +12702,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>447</v>
       </c>
@@ -11840,7 +12710,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>216</v>
       </c>
@@ -11848,7 +12718,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>201</v>
       </c>
@@ -11856,7 +12726,7 @@
         <v>907</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>287</v>
       </c>
@@ -11864,7 +12734,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>298</v>
       </c>
@@ -11872,7 +12742,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>332</v>
       </c>
@@ -11880,7 +12750,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>363</v>
       </c>
@@ -11888,7 +12758,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>225</v>
       </c>
@@ -11896,7 +12766,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>205</v>
       </c>
@@ -11904,7 +12774,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>209</v>
       </c>
@@ -11912,7 +12782,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>265</v>
       </c>
@@ -11920,7 +12790,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>262</v>
       </c>
@@ -11928,7 +12798,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>326</v>
       </c>
@@ -11936,7 +12806,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>385</v>
       </c>
@@ -11944,7 +12814,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>360</v>
       </c>
@@ -11952,7 +12822,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>357</v>
       </c>
@@ -11960,7 +12830,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>394</v>
       </c>
@@ -11968,7 +12838,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>434</v>
       </c>
@@ -11976,7 +12846,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>343</v>
       </c>
@@ -11984,7 +12854,7 @@
         <v>923</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>455</v>
       </c>
@@ -11992,7 +12862,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>401</v>
       </c>
@@ -12000,7 +12870,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>465</v>
       </c>
@@ -12008,7 +12878,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>283</v>
       </c>
@@ -12016,7 +12886,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>438</v>
       </c>
@@ -12024,7 +12894,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>222</v>
       </c>
@@ -12032,7 +12902,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>370</v>
       </c>
@@ -12040,7 +12910,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>372</v>
       </c>
@@ -12048,7 +12918,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>301</v>
       </c>
@@ -12056,7 +12926,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>339</v>
       </c>
@@ -12064,7 +12934,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>426</v>
       </c>
@@ -12072,7 +12942,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>311</v>
       </c>
@@ -12080,7 +12950,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>345</v>
       </c>
@@ -12088,7 +12958,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>295</v>
       </c>
@@ -12096,7 +12966,7 @@
         <v>937</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>329</v>
       </c>
@@ -12104,7 +12974,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>436</v>
       </c>
@@ -12112,7 +12982,7 @@
         <v>939</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>253</v>
       </c>
@@ -12120,7 +12990,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>440</v>
       </c>
@@ -12128,7 +12998,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>398</v>
       </c>
@@ -12136,7 +13006,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>228</v>
       </c>
@@ -12144,7 +13014,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>293</v>
       </c>
@@ -12152,7 +13022,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>428</v>
       </c>
@@ -12160,7 +13030,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>378</v>
       </c>
@@ -12168,7 +13038,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>407</v>
       </c>
@@ -12176,7 +13046,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>305</v>
       </c>
@@ -12184,7 +13054,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>281</v>
       </c>
@@ -12192,7 +13062,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>404</v>
       </c>
@@ -12200,7 +13070,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>313</v>
       </c>
@@ -12208,7 +13078,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>271</v>
       </c>
@@ -12216,7 +13086,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>445</v>
       </c>
@@ -12224,7 +13094,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>422</v>
       </c>
@@ -12232,7 +13102,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>259</v>
       </c>
@@ -12240,7 +13110,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>347</v>
       </c>
@@ -12248,7 +13118,7 @@
         <v>956</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>322</v>
       </c>
@@ -12256,7 +13126,7 @@
         <v>957</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>290</v>
       </c>
@@ -12264,7 +13134,7 @@
         <v>958</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>431</v>
       </c>
@@ -12272,7 +13142,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>413</v>
       </c>
@@ -12280,7 +13150,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>367</v>
       </c>
@@ -12288,7 +13158,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>382</v>
       </c>
@@ -12296,7 +13166,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>316</v>
       </c>
@@ -12304,7 +13174,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>242</v>
       </c>
@@ -12312,7 +13182,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>246</v>
       </c>
@@ -12320,7 +13190,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>268</v>
       </c>
@@ -12328,7 +13198,7 @@
         <v>966</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>443</v>
       </c>
@@ -12336,7 +13206,7 @@
         <v>967</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>451</v>
       </c>
@@ -12344,7 +13214,7 @@
         <v>968</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>172</v>
       </c>
@@ -12352,7 +13222,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>353</v>
       </c>
@@ -12360,7 +13230,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>308</v>
       </c>
@@ -12368,7 +13238,7 @@
         <v>971</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>249</v>
       </c>
@@ -12376,7 +13246,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>231</v>
       </c>
@@ -12384,7 +13254,7 @@
         <v>973</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>416</v>
       </c>
@@ -12392,7 +13262,7 @@
         <v>974</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>278</v>
       </c>
@@ -12400,7 +13270,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>375</v>
       </c>
@@ -12408,7 +13278,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>421</v>
       </c>
@@ -12416,7 +13286,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>388</v>
       </c>
@@ -12424,7 +13294,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>461</v>
       </c>
@@ -12432,7 +13302,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>274</v>
       </c>
@@ -12440,7 +13310,7 @@
         <v>980</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>238</v>
       </c>
@@ -12448,7 +13318,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>350</v>
       </c>
@@ -12464,9 +13334,9 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:CI5"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:87" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>219</v>
       </c>
@@ -12729,7 +13599,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="2" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:87" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>220</v>
       </c>
@@ -12992,7 +13862,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="3" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:87" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1031</v>
       </c>
@@ -13255,7 +14125,7 @@
         <v>1078</v>
       </c>
     </row>
-    <row r="4" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:87" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>1079</v>
       </c>
@@ -13518,7 +14388,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="5" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:87" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>441</v>
       </c>
@@ -13790,7 +14660,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet11"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -13799,9 +14669,9 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:B88"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>14</v>
       </c>
@@ -13809,7 +14679,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>219</v>
       </c>
@@ -13817,7 +14687,7 @@
         <v>1171</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>319</v>
       </c>
@@ -13825,7 +14695,7 @@
         <v>1172</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>410</v>
       </c>
@@ -13833,7 +14703,7 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>336</v>
       </c>
@@ -13841,7 +14711,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>458</v>
       </c>
@@ -13849,7 +14719,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>256</v>
       </c>
@@ -13857,7 +14727,7 @@
         <v>1174</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>391</v>
       </c>
@@ -13865,7 +14735,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>206</v>
       </c>
@@ -13873,7 +14743,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>167</v>
       </c>
@@ -13881,7 +14751,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>418</v>
       </c>
@@ -13889,7 +14759,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>447</v>
       </c>
@@ -13897,7 +14767,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>216</v>
       </c>
@@ -13905,7 +14775,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>201</v>
       </c>
@@ -13913,7 +14783,7 @@
         <v>1177</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>287</v>
       </c>
@@ -13921,7 +14791,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>298</v>
       </c>
@@ -13929,7 +14799,7 @@
         <v>1179</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>332</v>
       </c>
@@ -13937,7 +14807,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>363</v>
       </c>
@@ -13945,7 +14815,7 @@
         <v>1181</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>225</v>
       </c>
@@ -13953,7 +14823,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>205</v>
       </c>
@@ -13961,7 +14831,7 @@
         <v>1183</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>209</v>
       </c>
@@ -13969,7 +14839,7 @@
         <v>1184</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>265</v>
       </c>
@@ -13977,7 +14847,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>262</v>
       </c>
@@ -13985,7 +14855,7 @@
         <v>1186</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>326</v>
       </c>
@@ -13993,7 +14863,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>385</v>
       </c>
@@ -14001,7 +14871,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>360</v>
       </c>
@@ -14009,7 +14879,7 @@
         <v>1188</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>357</v>
       </c>
@@ -14017,7 +14887,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>394</v>
       </c>
@@ -14025,7 +14895,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>434</v>
       </c>
@@ -14033,7 +14903,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>343</v>
       </c>
@@ -14041,7 +14911,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>455</v>
       </c>
@@ -14049,7 +14919,7 @@
         <v>1191</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>401</v>
       </c>
@@ -14057,7 +14927,7 @@
         <v>1192</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>283</v>
       </c>
@@ -14065,7 +14935,7 @@
         <v>1193</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>438</v>
       </c>
@@ -14073,7 +14943,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>222</v>
       </c>
@@ -14081,7 +14951,7 @@
         <v>1194</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>370</v>
       </c>
@@ -14089,7 +14959,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>372</v>
       </c>
@@ -14097,7 +14967,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>301</v>
       </c>
@@ -14105,7 +14975,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>339</v>
       </c>
@@ -14113,7 +14983,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>426</v>
       </c>
@@ -14121,7 +14991,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>311</v>
       </c>
@@ -14129,7 +14999,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>345</v>
       </c>
@@ -14137,7 +15007,7 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>295</v>
       </c>
@@ -14145,7 +15015,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>329</v>
       </c>
@@ -14153,7 +15023,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>436</v>
       </c>
@@ -14161,7 +15031,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>253</v>
       </c>
@@ -14169,7 +15039,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>440</v>
       </c>
@@ -14177,7 +15047,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>398</v>
       </c>
@@ -14185,7 +15055,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>228</v>
       </c>
@@ -14193,7 +15063,7 @@
         <v>1203</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>293</v>
       </c>
@@ -14201,7 +15071,7 @@
         <v>1204</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>428</v>
       </c>
@@ -14209,7 +15079,7 @@
         <v>1205</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>378</v>
       </c>
@@ -14217,7 +15087,7 @@
         <v>1206</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>407</v>
       </c>
@@ -14225,7 +15095,7 @@
         <v>1207</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>305</v>
       </c>
@@ -14233,7 +15103,7 @@
         <v>1208</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>281</v>
       </c>
@@ -14241,7 +15111,7 @@
         <v>1209</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>404</v>
       </c>
@@ -14249,7 +15119,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>313</v>
       </c>
@@ -14257,7 +15127,7 @@
         <v>1211</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>271</v>
       </c>
@@ -14265,7 +15135,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>445</v>
       </c>
@@ -14273,7 +15143,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>422</v>
       </c>
@@ -14281,7 +15151,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>259</v>
       </c>
@@ -14289,7 +15159,7 @@
         <v>1212</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>347</v>
       </c>
@@ -14297,7 +15167,7 @@
         <v>1213</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>322</v>
       </c>
@@ -14305,7 +15175,7 @@
         <v>1214</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>290</v>
       </c>
@@ -14313,7 +15183,7 @@
         <v>1215</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>431</v>
       </c>
@@ -14321,7 +15191,7 @@
         <v>1216</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>413</v>
       </c>
@@ -14329,7 +15199,7 @@
         <v>1217</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>367</v>
       </c>
@@ -14337,7 +15207,7 @@
         <v>1218</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>382</v>
       </c>
@@ -14345,7 +15215,7 @@
         <v>1219</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>316</v>
       </c>
@@ -14353,7 +15223,7 @@
         <v>1220</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>242</v>
       </c>
@@ -14361,7 +15231,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>246</v>
       </c>
@@ -14369,7 +15239,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>268</v>
       </c>
@@ -14377,7 +15247,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>443</v>
       </c>
@@ -14385,7 +15255,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>451</v>
       </c>
@@ -14393,7 +15263,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>172</v>
       </c>
@@ -14401,7 +15271,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>353</v>
       </c>
@@ -14409,7 +15279,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>308</v>
       </c>
@@ -14417,7 +15287,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>249</v>
       </c>
@@ -14425,7 +15295,7 @@
         <v>1226</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>231</v>
       </c>
@@ -14433,7 +15303,7 @@
         <v>1227</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>416</v>
       </c>
@@ -14441,7 +15311,7 @@
         <v>1228</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>278</v>
       </c>
@@ -14449,7 +15319,7 @@
         <v>1229</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>375</v>
       </c>
@@ -14457,7 +15327,7 @@
         <v>1230</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>421</v>
       </c>
@@ -14465,7 +15335,7 @@
         <v>1231</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>388</v>
       </c>
@@ -14473,7 +15343,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>461</v>
       </c>
@@ -14481,7 +15351,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>274</v>
       </c>
@@ -14489,7 +15359,7 @@
         <v>1233</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>238</v>
       </c>
@@ -14497,7 +15367,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>350</v>
       </c>
@@ -14513,9 +15383,9 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>1236</v>
       </c>
@@ -14523,7 +15393,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>381</v>
       </c>
@@ -14531,7 +15401,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>397</v>
       </c>
@@ -14539,7 +15409,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>356</v>
       </c>
@@ -14547,7 +15417,7 @@
         <v>1239</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>342</v>
       </c>
@@ -14555,7 +15425,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>261</v>
       </c>
@@ -14563,7 +15433,7 @@
         <v>1240</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>200</v>
       </c>
@@ -14571,7 +15441,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>366</v>
       </c>
@@ -14579,7 +15449,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>425</v>
       </c>
@@ -14587,7 +15457,7 @@
         <v>1241</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>52</v>
       </c>
@@ -14603,16 +15473,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E87AAE7-287E-4577-93A9-75A189F69CE8}">
   <dimension ref="B2:G2"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="3" width="15.6640625" customWidth="1"/>
-    <col min="4" max="4" width="79.88671875" customWidth="1"/>
-    <col min="5" max="5" width="27.44140625" customWidth="1"/>
-    <col min="6" max="6" width="16.44140625" customWidth="1"/>
-    <col min="7" max="7" width="25.109375" customWidth="1"/>
+    <col min="2" max="3" width="15.7109375" customWidth="1"/>
+    <col min="4" max="4" width="79.85546875" customWidth="1"/>
+    <col min="5" max="5" width="27.42578125" customWidth="1"/>
+    <col min="6" max="6" width="16.42578125" customWidth="1"/>
+    <col min="7" max="7" width="25.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B2" s="50" t="s">
         <v>33</v>
       </c>
@@ -14649,20 +15519,20 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B1:T33"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="50.5546875" customWidth="1"/>
-    <col min="6" max="6" width="19.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="100.44140625" customWidth="1"/>
+    <col min="2" max="2" width="50.5703125" customWidth="1"/>
+    <col min="6" max="6" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="100.42578125" customWidth="1"/>
     <col min="11" max="14" width="20" customWidth="1"/>
-    <col min="16" max="16" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="29.88671875" customWidth="1"/>
-    <col min="20" max="20" width="39.88671875" customWidth="1"/>
+    <col min="16" max="16" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="29.85546875" customWidth="1"/>
+    <col min="20" max="20" width="39.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:20" ht="13.8" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:20" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:20" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:20" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B2" s="71" t="s">
         <v>39</v>
       </c>
@@ -14691,7 +15561,7 @@
       </c>
       <c r="T2" s="152"/>
     </row>
-    <row r="3" spans="2:20" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:20" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B3" s="111" t="s">
         <v>46</v>
       </c>
@@ -14732,7 +15602,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="4" spans="2:20" ht="93" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:20" ht="90" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B4" s="111" t="s">
         <v>58</v>
       </c>
@@ -14773,7 +15643,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="5" spans="2:20" ht="81.599999999999994" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:20" ht="90" x14ac:dyDescent="0.2">
       <c r="B5" s="111" t="s">
         <v>68</v>
       </c>
@@ -14814,7 +15684,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="6" spans="2:20" ht="86.4" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:20" ht="101.25" x14ac:dyDescent="0.2">
       <c r="B6" s="111" t="s">
         <v>78</v>
       </c>
@@ -14855,7 +15725,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="7" spans="2:20" ht="72" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:20" ht="79.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B7" s="111" t="s">
         <v>88</v>
       </c>
@@ -14887,7 +15757,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="8" spans="2:20" ht="82.2" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:20" ht="90.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B8" s="111" t="s">
         <v>95</v>
       </c>
@@ -14913,127 +15783,127 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="2:20" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:20" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="111" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="10" spans="2:20" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:20" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="111" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="11" spans="2:20" ht="97.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:20" ht="97.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="111" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="12" spans="2:20" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:20" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="111" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="13" spans="2:20" ht="87" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:20" ht="87" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="111" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="14" spans="2:20" ht="87.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:20" ht="87.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="111" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="15" spans="2:20" ht="87.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:20" ht="87.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="111" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="16" spans="2:20" ht="87.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:20" ht="87.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="111" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="17" spans="2:2" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:2" ht="50.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B17" s="111" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="18" spans="2:2" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:2" ht="50.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B18" s="111" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="19" spans="2:2" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:2" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B19" s="111" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="20" spans="2:2" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:2" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B20" s="111" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="21" spans="2:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B21" s="111" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="22" spans="2:2" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:2" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B22" s="111" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="23" spans="2:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B23" s="111" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="24" spans="2:2" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:2" ht="50.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B24" s="111" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="25" spans="2:2" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:2" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B25" s="111" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="26" spans="2:2" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:2" ht="50.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B26" s="111" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="27" spans="2:2" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:2" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B27" s="111" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="28" spans="2:2" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:2" ht="50.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B28" s="111" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="29" spans="2:2" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:2" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B29" s="111" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="30" spans="2:2" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:2" ht="50.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B30" s="111" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="31" spans="2:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B31" s="111" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="32" spans="2:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B32" s="111" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="33" spans="2:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B33" s="112" t="s">
         <v>125</v>
       </c>
@@ -15062,18 +15932,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="B1:P50"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="47.88671875" customWidth="1"/>
+    <col min="2" max="2" width="47.85546875" customWidth="1"/>
     <col min="3" max="3" width="56" style="24" customWidth="1"/>
-    <col min="4" max="4" width="5.44140625" customWidth="1"/>
+    <col min="4" max="4" width="5.42578125" customWidth="1"/>
     <col min="7" max="8" width="44" customWidth="1"/>
-    <col min="9" max="9" width="10.33203125" customWidth="1"/>
-    <col min="10" max="16" width="17.5546875" customWidth="1"/>
-    <col min="17" max="18" width="10.33203125" customWidth="1"/>
+    <col min="9" max="9" width="10.28515625" customWidth="1"/>
+    <col min="10" max="16" width="17.5703125" customWidth="1"/>
+    <col min="17" max="18" width="10.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:16" ht="124.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="2:16" ht="124.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B1" s="47" t="s">
         <v>126</v>
       </c>
@@ -15095,12 +15965,12 @@
       <c r="L1" s="158" t="s">
         <v>50</v>
       </c>
-      <c r="M1" s="121"/>
-      <c r="N1" s="121"/>
-      <c r="O1" s="121"/>
-      <c r="P1" s="122"/>
-    </row>
-    <row r="2" spans="2:16" ht="124.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="120"/>
+    </row>
+    <row r="2" spans="2:16" ht="124.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B2" s="45" t="s">
         <v>128</v>
       </c>
@@ -15135,7 +16005,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="2:16" ht="124.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="3" spans="2:16" ht="124.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B3" s="41" t="s">
         <v>131</v>
       </c>
@@ -15174,7 +16044,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="2:16" ht="124.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="4" spans="2:16" ht="124.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B4" s="41" t="s">
         <v>134</v>
       </c>
@@ -15211,7 +16081,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="2:16" ht="124.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="5" spans="2:16" ht="124.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B5" s="38" t="s">
         <v>137</v>
       </c>
@@ -15248,7 +16118,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="2:16" ht="124.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="2:16" ht="124.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
       <c r="B6" s="41" t="s">
         <v>140</v>
       </c>
@@ -15285,7 +16155,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="2:16" ht="124.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="2:16" ht="124.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B7" s="38" t="s">
         <v>143</v>
       </c>
@@ -15318,7 +16188,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="2:16" ht="124.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:16" ht="124.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="41" t="s">
         <v>144</v>
       </c>
@@ -15339,7 +16209,7 @@
       <c r="O8" s="25"/>
       <c r="P8" s="25"/>
     </row>
-    <row r="9" spans="2:16" ht="124.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:16" ht="124.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="38" t="s">
         <v>145</v>
       </c>
@@ -15364,7 +16234,7 @@
       <c r="O9" s="156"/>
       <c r="P9" s="156"/>
     </row>
-    <row r="10" spans="2:16" ht="124.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:16" ht="124.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
       <c r="B10" s="41" t="s">
         <v>147</v>
       </c>
@@ -15383,13 +16253,13 @@
       <c r="K10" s="157" t="s">
         <v>149</v>
       </c>
-      <c r="L10" s="121"/>
-      <c r="M10" s="121"/>
-      <c r="N10" s="121"/>
-      <c r="O10" s="121"/>
-      <c r="P10" s="122"/>
-    </row>
-    <row r="11" spans="2:16" ht="124.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L10" s="119"/>
+      <c r="M10" s="119"/>
+      <c r="N10" s="119"/>
+      <c r="O10" s="119"/>
+      <c r="P10" s="120"/>
+    </row>
+    <row r="11" spans="2:16" ht="124.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="38" t="s">
         <v>150</v>
       </c>
@@ -15408,13 +16278,13 @@
       <c r="K11" s="157" t="s">
         <v>152</v>
       </c>
-      <c r="L11" s="121"/>
-      <c r="M11" s="121"/>
-      <c r="N11" s="121"/>
-      <c r="O11" s="121"/>
-      <c r="P11" s="122"/>
-    </row>
-    <row r="12" spans="2:16" ht="124.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L11" s="119"/>
+      <c r="M11" s="119"/>
+      <c r="N11" s="119"/>
+      <c r="O11" s="119"/>
+      <c r="P11" s="120"/>
+    </row>
+    <row r="12" spans="2:16" ht="124.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="41" t="s">
         <v>153</v>
       </c>
@@ -15433,13 +16303,13 @@
       <c r="K12" s="157" t="s">
         <v>155</v>
       </c>
-      <c r="L12" s="121"/>
-      <c r="M12" s="121"/>
-      <c r="N12" s="121"/>
-      <c r="O12" s="121"/>
-      <c r="P12" s="122"/>
-    </row>
-    <row r="13" spans="2:16" ht="124.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L12" s="119"/>
+      <c r="M12" s="119"/>
+      <c r="N12" s="119"/>
+      <c r="O12" s="119"/>
+      <c r="P12" s="120"/>
+    </row>
+    <row r="13" spans="2:16" ht="124.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="38" t="s">
         <v>156</v>
       </c>
@@ -15458,13 +16328,13 @@
       <c r="K13" s="157" t="s">
         <v>158</v>
       </c>
-      <c r="L13" s="121"/>
-      <c r="M13" s="121"/>
-      <c r="N13" s="121"/>
-      <c r="O13" s="121"/>
-      <c r="P13" s="122"/>
-    </row>
-    <row r="14" spans="2:16" ht="124.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L13" s="119"/>
+      <c r="M13" s="119"/>
+      <c r="N13" s="119"/>
+      <c r="O13" s="119"/>
+      <c r="P13" s="120"/>
+    </row>
+    <row r="14" spans="2:16" ht="124.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="38" t="s">
         <v>159</v>
       </c>
@@ -15485,7 +16355,7 @@
       <c r="O14" s="25"/>
       <c r="P14" s="25"/>
     </row>
-    <row r="15" spans="2:16" ht="124.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:16" ht="124.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="38" t="s">
         <v>160</v>
       </c>
@@ -15506,7 +16376,7 @@
       <c r="O15" s="25"/>
       <c r="P15" s="25"/>
     </row>
-    <row r="16" spans="2:16" ht="124.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:16" ht="124.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="38" t="s">
         <v>161</v>
       </c>
@@ -15527,7 +16397,7 @@
       <c r="O16" s="25"/>
       <c r="P16" s="25"/>
     </row>
-    <row r="17" spans="2:16" ht="124.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:16" ht="124.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="38" t="s">
         <v>162</v>
       </c>
@@ -15548,7 +16418,7 @@
       <c r="O17" s="25"/>
       <c r="P17" s="25"/>
     </row>
-    <row r="18" spans="2:16" ht="124.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:16" ht="124.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="38" t="s">
         <v>163</v>
       </c>
@@ -15569,7 +16439,7 @@
       <c r="O18" s="25"/>
       <c r="P18" s="25"/>
     </row>
-    <row r="19" spans="2:16" ht="124.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:16" ht="124.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="38" t="s">
         <v>164</v>
       </c>
@@ -15590,7 +16460,7 @@
       <c r="O19" s="25"/>
       <c r="P19" s="25"/>
     </row>
-    <row r="20" spans="2:16" ht="124.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:16" ht="124.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="38" t="s">
         <v>165</v>
       </c>
@@ -15611,7 +16481,7 @@
       <c r="O20" s="25"/>
       <c r="P20" s="25"/>
     </row>
-    <row r="21" spans="2:16" ht="124.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:16" ht="124.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="41" t="s">
         <v>166</v>
       </c>
@@ -15632,7 +16502,7 @@
       <c r="O21" s="25"/>
       <c r="P21" s="25"/>
     </row>
-    <row r="22" spans="2:16" ht="124.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:16" ht="124.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="38" t="s">
         <v>167</v>
       </c>
@@ -15653,7 +16523,7 @@
       <c r="O22" s="25"/>
       <c r="P22" s="25"/>
     </row>
-    <row r="23" spans="2:16" ht="124.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:16" ht="124.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="41" t="s">
         <v>168</v>
       </c>
@@ -15674,7 +16544,7 @@
       <c r="O23" s="25"/>
       <c r="P23" s="25"/>
     </row>
-    <row r="24" spans="2:16" ht="124.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:16" ht="124.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="38" t="s">
         <v>169</v>
       </c>
@@ -15695,7 +16565,7 @@
       <c r="O24" s="25"/>
       <c r="P24" s="25"/>
     </row>
-    <row r="25" spans="2:16" ht="124.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:16" ht="124.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="38" t="s">
         <v>170</v>
       </c>
@@ -15716,7 +16586,7 @@
       <c r="O25" s="25"/>
       <c r="P25" s="25"/>
     </row>
-    <row r="26" spans="2:16" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:16" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="38" t="s">
         <v>171</v>
       </c>
@@ -15737,7 +16607,7 @@
       <c r="O26" s="25"/>
       <c r="P26" s="25"/>
     </row>
-    <row r="27" spans="2:16" ht="120" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:16" ht="120" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="41" t="s">
         <v>172</v>
       </c>
@@ -15758,7 +16628,7 @@
       <c r="O27" s="25"/>
       <c r="P27" s="25"/>
     </row>
-    <row r="28" spans="2:16" ht="99.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:16" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="38" t="s">
         <v>173</v>
       </c>
@@ -15779,7 +16649,7 @@
       <c r="O28" s="25"/>
       <c r="P28" s="25"/>
     </row>
-    <row r="29" spans="2:16" ht="120" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:16" ht="120" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="38" t="s">
         <v>174</v>
       </c>
@@ -15800,7 +16670,7 @@
       <c r="O29" s="25"/>
       <c r="P29" s="25"/>
     </row>
-    <row r="30" spans="2:16" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="38" t="s">
         <v>175</v>
       </c>
@@ -15821,7 +16691,7 @@
       <c r="O30" s="25"/>
       <c r="P30" s="25"/>
     </row>
-    <row r="31" spans="2:16" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="41" t="s">
         <v>176</v>
       </c>
@@ -15842,7 +16712,7 @@
       <c r="O31" s="25"/>
       <c r="P31" s="25"/>
     </row>
-    <row r="32" spans="2:16" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="38" t="s">
         <v>177</v>
       </c>
@@ -15863,7 +16733,7 @@
       <c r="O32" s="25"/>
       <c r="P32" s="25"/>
     </row>
-    <row r="33" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="41" t="s">
         <v>178</v>
       </c>
@@ -15882,7 +16752,7 @@
       <c r="O33" s="25"/>
       <c r="P33" s="25"/>
     </row>
-    <row r="34" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="38" t="s">
         <v>179</v>
       </c>
@@ -15901,7 +16771,7 @@
       <c r="O34" s="25"/>
       <c r="P34" s="25"/>
     </row>
-    <row r="35" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="41" t="s">
         <v>180</v>
       </c>
@@ -15920,7 +16790,7 @@
       <c r="O35" s="25"/>
       <c r="P35" s="25"/>
     </row>
-    <row r="36" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="38" t="s">
         <v>181</v>
       </c>
@@ -15939,7 +16809,7 @@
       <c r="O36" s="25"/>
       <c r="P36" s="25"/>
     </row>
-    <row r="37" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="41" t="s">
         <v>182</v>
       </c>
@@ -15958,7 +16828,7 @@
       <c r="O37" s="25"/>
       <c r="P37" s="25"/>
     </row>
-    <row r="38" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="41" t="s">
         <v>183</v>
       </c>
@@ -15977,7 +16847,7 @@
       <c r="O38" s="25"/>
       <c r="P38" s="25"/>
     </row>
-    <row r="39" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="38" t="s">
         <v>184</v>
       </c>
@@ -15996,7 +16866,7 @@
       <c r="O39" s="25"/>
       <c r="P39" s="25"/>
     </row>
-    <row r="40" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="41" t="s">
         <v>185</v>
       </c>
@@ -16015,7 +16885,7 @@
       <c r="O40" s="25"/>
       <c r="P40" s="25"/>
     </row>
-    <row r="41" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="38" t="s">
         <v>186</v>
       </c>
@@ -16034,7 +16904,7 @@
       <c r="O41" s="25"/>
       <c r="P41" s="25"/>
     </row>
-    <row r="42" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="41" t="s">
         <v>187</v>
       </c>
@@ -16053,7 +16923,7 @@
       <c r="O42" s="25"/>
       <c r="P42" s="25"/>
     </row>
-    <row r="43" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="38" t="s">
         <v>188</v>
       </c>
@@ -16072,7 +16942,7 @@
       <c r="O43" s="25"/>
       <c r="P43" s="25"/>
     </row>
-    <row r="44" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="41" t="s">
         <v>189</v>
       </c>
@@ -16091,7 +16961,7 @@
       <c r="O44" s="25"/>
       <c r="P44" s="25"/>
     </row>
-    <row r="45" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="38" t="s">
         <v>190</v>
       </c>
@@ -16110,7 +16980,7 @@
       <c r="O45" s="25"/>
       <c r="P45" s="25"/>
     </row>
-    <row r="46" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="41" t="s">
         <v>191</v>
       </c>
@@ -16129,7 +16999,7 @@
       <c r="O46" s="25"/>
       <c r="P46" s="25"/>
     </row>
-    <row r="47" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="38" t="s">
         <v>192</v>
       </c>
@@ -16148,7 +17018,7 @@
       <c r="O47" s="25"/>
       <c r="P47" s="25"/>
     </row>
-    <row r="48" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="41" t="s">
         <v>193</v>
       </c>
@@ -16167,7 +17037,7 @@
       <c r="O48" s="25"/>
       <c r="P48" s="25"/>
     </row>
-    <row r="49" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="38" t="s">
         <v>194</v>
       </c>
@@ -16186,7 +17056,7 @@
       <c r="O49" s="25"/>
       <c r="P49" s="25"/>
     </row>
-    <row r="50" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B50" s="25"/>
       <c r="C50" s="25"/>
       <c r="D50" s="25"/>
@@ -16229,19 +17099,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:AI117"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.44140625" style="53" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.109375" style="53" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.88671875" style="53" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="12.5546875" style="53" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="79.6640625" style="53" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="83.109375" style="53" hidden="1" customWidth="1"/>
-    <col min="7" max="9" width="8.6640625" style="53" customWidth="1"/>
-    <col min="10" max="16384" width="8.6640625" style="53"/>
+    <col min="1" max="1" width="22.42578125" style="53" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.140625" style="53" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.85546875" style="53" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5703125" style="53" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="79.7109375" style="53" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="83.140625" style="53" hidden="1" customWidth="1"/>
+    <col min="7" max="9" width="8.7109375" style="53" customWidth="1"/>
+    <col min="10" max="16384" width="8.7109375" style="53"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="54" t="s">
         <v>195</v>
       </c>
@@ -16261,7 +17131,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="114" t="s">
         <v>200</v>
       </c>
@@ -16281,7 +17151,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="114" t="s">
         <v>200</v>
       </c>
@@ -16301,7 +17171,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="114" t="s">
         <v>200</v>
       </c>
@@ -16321,7 +17191,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="114" t="s">
         <v>200</v>
       </c>
@@ -16341,7 +17211,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="114" t="s">
         <v>200</v>
       </c>
@@ -16361,7 +17231,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="114" t="s">
         <v>200</v>
       </c>
@@ -16381,7 +17251,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="114" t="s">
         <v>200</v>
       </c>
@@ -16401,7 +17271,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="114" t="s">
         <v>200</v>
       </c>
@@ -16421,7 +17291,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="114" t="s">
         <v>200</v>
       </c>
@@ -16441,7 +17311,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="114" t="s">
         <v>200</v>
       </c>
@@ -16461,7 +17331,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="114" t="s">
         <v>200</v>
       </c>
@@ -16481,7 +17351,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="114" t="s">
         <v>200</v>
       </c>
@@ -16501,7 +17371,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="114" t="s">
         <v>200</v>
       </c>
@@ -16521,7 +17391,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="114" t="s">
         <v>200</v>
       </c>
@@ -16541,7 +17411,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="114" t="s">
         <v>200</v>
       </c>
@@ -16561,7 +17431,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="114" t="s">
         <v>200</v>
       </c>
@@ -16581,7 +17451,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="114" t="s">
         <v>200</v>
       </c>
@@ -16601,7 +17471,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="114" t="s">
         <v>200</v>
       </c>
@@ -16621,7 +17491,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="114" t="s">
         <v>261</v>
       </c>
@@ -16641,7 +17511,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="114" t="s">
         <v>261</v>
       </c>
@@ -16661,7 +17531,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="114" t="s">
         <v>261</v>
       </c>
@@ -16681,7 +17551,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="114" t="s">
         <v>261</v>
       </c>
@@ -16701,7 +17571,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="114" t="s">
         <v>261</v>
       </c>
@@ -16721,7 +17591,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="114" t="s">
         <v>261</v>
       </c>
@@ -16741,7 +17611,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="114" t="s">
         <v>261</v>
       </c>
@@ -16761,7 +17631,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="114" t="s">
         <v>261</v>
       </c>
@@ -16781,7 +17651,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="114" t="s">
         <v>261</v>
       </c>
@@ -16801,7 +17671,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="114" t="s">
         <v>261</v>
       </c>
@@ -16821,7 +17691,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="114" t="s">
         <v>261</v>
       </c>
@@ -16841,7 +17711,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="114" t="s">
         <v>261</v>
       </c>
@@ -16861,7 +17731,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="114" t="s">
         <v>261</v>
       </c>
@@ -16881,7 +17751,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="114" t="s">
         <v>261</v>
       </c>
@@ -16901,7 +17771,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="114" t="s">
         <v>261</v>
       </c>
@@ -16921,7 +17791,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="114" t="s">
         <v>261</v>
       </c>
@@ -16941,7 +17811,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="114" t="s">
         <v>261</v>
       </c>
@@ -16961,7 +17831,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="114" t="s">
         <v>261</v>
       </c>
@@ -16981,7 +17851,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="114" t="s">
         <v>261</v>
       </c>
@@ -17001,7 +17871,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="114" t="s">
         <v>261</v>
       </c>
@@ -17021,7 +17891,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="114" t="s">
         <v>261</v>
       </c>
@@ -17041,7 +17911,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="114" t="s">
         <v>261</v>
       </c>
@@ -17061,7 +17931,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="114" t="s">
         <v>261</v>
       </c>
@@ -17081,7 +17951,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="114" t="s">
         <v>261</v>
       </c>
@@ -17101,7 +17971,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="114" t="s">
         <v>261</v>
       </c>
@@ -17121,7 +17991,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="114" t="s">
         <v>261</v>
       </c>
@@ -17141,7 +18011,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="114" t="s">
         <v>342</v>
       </c>
@@ -17161,7 +18031,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="114" t="s">
         <v>342</v>
       </c>
@@ -17181,7 +18051,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="114" t="s">
         <v>342</v>
       </c>
@@ -17201,7 +18071,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="114" t="s">
         <v>342</v>
       </c>
@@ -17221,7 +18091,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="114" t="s">
         <v>342</v>
       </c>
@@ -17241,7 +18111,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="114" t="s">
         <v>356</v>
       </c>
@@ -17261,7 +18131,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="114" t="s">
         <v>356</v>
       </c>
@@ -17281,7 +18151,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="114" t="s">
         <v>356</v>
       </c>
@@ -17301,7 +18171,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="114" t="s">
         <v>356</v>
       </c>
@@ -17321,7 +18191,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="114" t="s">
         <v>366</v>
       </c>
@@ -17341,7 +18211,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="114" t="s">
         <v>366</v>
       </c>
@@ -17361,7 +18231,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="114" t="s">
         <v>366</v>
       </c>
@@ -17381,7 +18251,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="114" t="s">
         <v>366</v>
       </c>
@@ -17401,7 +18271,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="114" t="s">
         <v>366</v>
       </c>
@@ -17421,7 +18291,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="114" t="s">
         <v>381</v>
       </c>
@@ -17441,7 +18311,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="114" t="s">
         <v>381</v>
       </c>
@@ -17461,7 +18331,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="114" t="s">
         <v>381</v>
       </c>
@@ -17481,7 +18351,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="114" t="s">
         <v>381</v>
       </c>
@@ -17501,7 +18371,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="114" t="s">
         <v>381</v>
       </c>
@@ -17521,7 +18391,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="114" t="s">
         <v>397</v>
       </c>
@@ -17541,7 +18411,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="114" t="s">
         <v>397</v>
       </c>
@@ -17561,7 +18431,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="114" t="s">
         <v>397</v>
       </c>
@@ -17581,7 +18451,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="114" t="s">
         <v>397</v>
       </c>
@@ -17601,7 +18471,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="114" t="s">
         <v>397</v>
       </c>
@@ -17621,7 +18491,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="114" t="s">
         <v>397</v>
       </c>
@@ -17641,7 +18511,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="114" t="s">
         <v>397</v>
       </c>
@@ -17661,7 +18531,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="114" t="s">
         <v>397</v>
       </c>
@@ -17681,7 +18551,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="114" t="s">
         <v>397</v>
       </c>
@@ -17701,7 +18571,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="114" t="s">
         <v>397</v>
       </c>
@@ -17721,7 +18591,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="114" t="s">
         <v>425</v>
       </c>
@@ -17741,7 +18611,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="114" t="s">
         <v>425</v>
       </c>
@@ -17761,7 +18631,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="114" t="s">
         <v>425</v>
       </c>
@@ -17781,7 +18651,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="114" t="s">
         <v>425</v>
       </c>
@@ -17801,7 +18671,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="114" t="s">
         <v>425</v>
       </c>
@@ -17821,7 +18691,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="114" t="s">
         <v>425</v>
       </c>
@@ -17841,7 +18711,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="81" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A81" s="114" t="s">
         <v>425</v>
       </c>
@@ -17890,7 +18760,7 @@
       <c r="AH81" s="114"/>
       <c r="AI81" s="114"/>
     </row>
-    <row r="82" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A82" s="114" t="s">
         <v>425</v>
       </c>
@@ -17939,7 +18809,7 @@
       <c r="AH82" s="114"/>
       <c r="AI82" s="114"/>
     </row>
-    <row r="83" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A83" s="114" t="s">
         <v>425</v>
       </c>
@@ -17988,7 +18858,7 @@
       <c r="AH83" s="114"/>
       <c r="AI83" s="114"/>
     </row>
-    <row r="84" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A84" s="114" t="s">
         <v>425</v>
       </c>
@@ -18037,7 +18907,7 @@
       <c r="AH84" s="114"/>
       <c r="AI84" s="114"/>
     </row>
-    <row r="85" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A85" s="114" t="s">
         <v>52</v>
       </c>
@@ -18086,7 +18956,7 @@
       <c r="AH85" s="114"/>
       <c r="AI85" s="114"/>
     </row>
-    <row r="86" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A86" s="114" t="s">
         <v>52</v>
       </c>
@@ -18135,7 +19005,7 @@
       <c r="AH86" s="114"/>
       <c r="AI86" s="114"/>
     </row>
-    <row r="87" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A87" s="114" t="s">
         <v>52</v>
       </c>
@@ -18184,7 +19054,7 @@
       <c r="AH87" s="114"/>
       <c r="AI87" s="114"/>
     </row>
-    <row r="88" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A88" s="114" t="s">
         <v>52</v>
       </c>
@@ -18233,7 +19103,7 @@
       <c r="AH88" s="114"/>
       <c r="AI88" s="114"/>
     </row>
-    <row r="90" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A90" s="114"/>
       <c r="B90" s="114"/>
       <c r="C90" s="114"/>
@@ -18270,7 +19140,7 @@
       <c r="AH90" s="114"/>
       <c r="AI90" s="114"/>
     </row>
-    <row r="91" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A91" s="59" t="s">
         <v>464</v>
       </c>
@@ -18282,13 +19152,13 @@
         <f t="array" ref="D91:D99">_xlfn.UNIQUE(A2:A88)</f>
         <v>Mecanico</v>
       </c>
-      <c r="E91" s="110" t="str">
+      <c r="E91" s="110" t="e" vm="1">
         <f t="array" ref="E91:E116">_xlfn._xlws.FILTER(B2:B88, A2:A88='RA Form'!D8)</f>
-        <v>Bordes afilados</v>
-      </c>
-      <c r="F91" s="109" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="F91" s="109" t="e" vm="1">
         <f t="array" ref="F91">_xlfn._xlws.FILTER(C2:C88, B2:B88='RA Form'!E8)</f>
-        <v>Amputación</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G91" s="108" t="e" vm="1">
         <f t="array" ref="G91:G92">_xlfn._xlws.FILTER(E2:E88, C2:C88='RA Form'!F8)</f>
@@ -18326,7 +19196,7 @@
       <c r="AH91" s="109"/>
       <c r="AI91" s="109"/>
     </row>
-    <row r="92" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A92" s="114" t="s">
         <v>466</v>
       </c>
@@ -18337,8 +19207,8 @@
       <c r="D92" s="109" t="str">
         <v>Lugar de trabajo</v>
       </c>
-      <c r="E92" s="109" t="str">
-        <v>Cargas en movimiento</v>
+      <c r="E92" s="109" t="e" vm="1">
+        <v>#VALUE!</v>
       </c>
       <c r="F92" s="109"/>
       <c r="G92" s="108" t="e" vm="1">
@@ -18373,7 +19243,7 @@
       <c r="AH92" s="109"/>
       <c r="AI92" s="109"/>
     </row>
-    <row r="93" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A93" s="114" t="s">
         <v>467</v>
       </c>
@@ -18384,8 +19254,8 @@
       <c r="D93" s="109" t="str">
         <v>Herramientas</v>
       </c>
-      <c r="E93" s="109" t="str">
-        <v>Cargas inestables</v>
+      <c r="E93" s="109" t="e" vm="1">
+        <v>#VALUE!</v>
       </c>
       <c r="F93" s="109"/>
       <c r="G93" s="108"/>
@@ -18418,7 +19288,7 @@
       <c r="AH93" s="109"/>
       <c r="AI93" s="109"/>
     </row>
-    <row r="94" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A94" s="114" t="s">
         <v>468</v>
       </c>
@@ -18429,8 +19299,8 @@
       <c r="D94" s="109" t="str">
         <v>Eléctrico</v>
       </c>
-      <c r="E94" s="109" t="str">
-        <v>Aplastamiento</v>
+      <c r="E94" s="109" t="e" vm="1">
+        <v>#VALUE!</v>
       </c>
       <c r="F94" s="109"/>
       <c r="G94" s="108"/>
@@ -18463,15 +19333,15 @@
       <c r="AH94" s="109"/>
       <c r="AI94" s="109"/>
     </row>
-    <row r="95" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A95" s="114"/>
       <c r="B95" s="114"/>
       <c r="C95" s="109"/>
       <c r="D95" s="109" t="str">
         <v>Psicosocial</v>
       </c>
-      <c r="E95" s="109" t="str">
-        <v>Atrapamiento</v>
+      <c r="E95" s="109" t="e" vm="1">
+        <v>#VALUE!</v>
       </c>
       <c r="F95" s="109"/>
       <c r="G95" s="108"/>
@@ -18504,15 +19374,15 @@
       <c r="AH95" s="109"/>
       <c r="AI95" s="109"/>
     </row>
-    <row r="96" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A96" s="114"/>
       <c r="B96" s="114"/>
       <c r="C96" s="109"/>
       <c r="D96" s="109" t="str">
         <v>Actividades de trabajo</v>
       </c>
-      <c r="E96" s="109" t="str">
-        <v>Abrasión/fricción</v>
+      <c r="E96" s="109" t="e" vm="1">
+        <v>#VALUE!</v>
       </c>
       <c r="F96" s="109"/>
       <c r="G96" s="108"/>
@@ -18545,7 +19415,7 @@
       <c r="AH96" s="109"/>
       <c r="AI96" s="109"/>
     </row>
-    <row r="97" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A97" s="59" t="s">
         <v>469</v>
       </c>
@@ -18554,8 +19424,8 @@
       <c r="D97" s="109" t="str">
         <v>Ergonomía</v>
       </c>
-      <c r="E97" s="109" t="str">
-        <v>Eyección de material</v>
+      <c r="E97" s="109" t="e" vm="1">
+        <v>#VALUE!</v>
       </c>
       <c r="F97" s="109"/>
       <c r="G97" s="109"/>
@@ -18588,7 +19458,7 @@
       <c r="AH97" s="109"/>
       <c r="AI97" s="109"/>
     </row>
-    <row r="98" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A98" s="114">
         <v>1</v>
       </c>
@@ -18597,8 +19467,8 @@
       <c r="D98" s="109" t="str">
         <v>Químicos</v>
       </c>
-      <c r="E98" s="109" t="str">
-        <v>Carga suspendida</v>
+      <c r="E98" s="109" t="e" vm="1">
+        <v>#VALUE!</v>
       </c>
       <c r="F98" s="109"/>
       <c r="G98" s="109"/>
@@ -18631,7 +19501,7 @@
       <c r="AH98" s="109"/>
       <c r="AI98" s="109"/>
     </row>
-    <row r="99" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A99" s="114">
         <v>2</v>
       </c>
@@ -18640,8 +19510,8 @@
       <c r="D99" s="109" t="str">
         <v>Seguridad</v>
       </c>
-      <c r="E99" s="109" t="str">
-        <v>Liberación de energía</v>
+      <c r="E99" s="109" t="e" vm="1">
+        <v>#VALUE!</v>
       </c>
       <c r="F99" s="109"/>
       <c r="G99" s="109"/>
@@ -18674,15 +19544,15 @@
       <c r="AH99" s="109"/>
       <c r="AI99" s="109"/>
     </row>
-    <row r="100" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A100" s="114">
         <v>3</v>
       </c>
       <c r="B100" s="114"/>
       <c r="C100" s="109"/>
       <c r="D100" s="109"/>
-      <c r="E100" s="109" t="str">
-        <v>Superficie caliente/fría</v>
+      <c r="E100" s="109" t="e" vm="1">
+        <v>#VALUE!</v>
       </c>
       <c r="F100" s="109"/>
       <c r="G100" s="109"/>
@@ -18715,15 +19585,15 @@
       <c r="AH100" s="109"/>
       <c r="AI100" s="109"/>
     </row>
-    <row r="101" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A101" s="114">
         <v>4</v>
       </c>
       <c r="B101" s="114"/>
       <c r="C101" s="109"/>
       <c r="D101" s="109"/>
-      <c r="E101" s="109" t="str">
-        <v>Ruido</v>
+      <c r="E101" s="109" t="e" vm="1">
+        <v>#VALUE!</v>
       </c>
       <c r="F101" s="109"/>
       <c r="G101" s="109"/>
@@ -18756,15 +19626,15 @@
       <c r="AH101" s="109"/>
       <c r="AI101" s="109"/>
     </row>
-    <row r="102" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A102" s="114">
         <v>5</v>
       </c>
       <c r="B102" s="114"/>
       <c r="C102" s="109"/>
       <c r="D102" s="109"/>
-      <c r="E102" s="109" t="str">
-        <v>Vibración</v>
+      <c r="E102" s="109" t="e" vm="1">
+        <v>#VALUE!</v>
       </c>
       <c r="F102" s="109"/>
       <c r="G102" s="109"/>
@@ -18797,13 +19667,13 @@
       <c r="AH102" s="109"/>
       <c r="AI102" s="109"/>
     </row>
-    <row r="103" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A103" s="114"/>
       <c r="B103" s="114"/>
       <c r="C103" s="109"/>
       <c r="D103" s="109"/>
-      <c r="E103" s="109" t="str">
-        <v>Radiación ionizante</v>
+      <c r="E103" s="109" t="e" vm="1">
+        <v>#VALUE!</v>
       </c>
       <c r="F103" s="109"/>
       <c r="G103" s="109"/>
@@ -18836,13 +19706,13 @@
       <c r="AH103" s="109"/>
       <c r="AI103" s="109"/>
     </row>
-    <row r="104" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A104" s="114"/>
       <c r="B104" s="114"/>
       <c r="C104" s="109"/>
       <c r="D104" s="109"/>
-      <c r="E104" s="109" t="str">
-        <v>Radiación no ionizante</v>
+      <c r="E104" s="109" t="e" vm="1">
+        <v>#VALUE!</v>
       </c>
       <c r="F104" s="109"/>
       <c r="G104" s="109"/>
@@ -18875,13 +19745,13 @@
       <c r="AH104" s="109"/>
       <c r="AI104" s="109"/>
     </row>
-    <row r="105" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A105" s="114"/>
       <c r="B105" s="114"/>
       <c r="C105" s="109"/>
       <c r="D105" s="109"/>
-      <c r="E105" s="109" t="str">
-        <v>Sistema de presión</v>
+      <c r="E105" s="109" t="e" vm="1">
+        <v>#VALUE!</v>
       </c>
       <c r="F105" s="109"/>
       <c r="G105" s="109"/>
@@ -18914,15 +19784,15 @@
       <c r="AH105" s="109"/>
       <c r="AI105" s="109"/>
     </row>
-    <row r="106" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A106" s="109" t="s">
         <v>470</v>
       </c>
       <c r="B106" s="114"/>
       <c r="C106" s="109"/>
       <c r="D106" s="109"/>
-      <c r="E106" s="109" t="str">
-        <v>Inyección por presión</v>
+      <c r="E106" s="109" t="e" vm="1">
+        <v>#VALUE!</v>
       </c>
       <c r="F106" s="109"/>
       <c r="G106" s="109"/>
@@ -18955,15 +19825,15 @@
       <c r="AH106" s="109"/>
       <c r="AI106" s="109"/>
     </row>
-    <row r="107" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A107" s="109" t="s">
         <v>471</v>
       </c>
       <c r="B107" s="114"/>
       <c r="C107" s="109"/>
       <c r="D107" s="109"/>
-      <c r="E107" s="109" t="str">
-        <v>Alta o baja presión</v>
+      <c r="E107" s="109" t="e" vm="1">
+        <v>#VALUE!</v>
       </c>
       <c r="F107" s="109"/>
       <c r="G107" s="109"/>
@@ -18996,13 +19866,13 @@
       <c r="AH107" s="109"/>
       <c r="AI107" s="109"/>
     </row>
-    <row r="108" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A108" s="114"/>
       <c r="B108" s="114"/>
       <c r="C108" s="109"/>
       <c r="D108" s="109"/>
-      <c r="E108" s="109" t="str">
-        <v>Partes móviles</v>
+      <c r="E108" s="109" t="e" vm="1">
+        <v>#VALUE!</v>
       </c>
       <c r="F108" s="109"/>
       <c r="G108" s="109"/>
@@ -19035,13 +19905,13 @@
       <c r="AH108" s="109"/>
       <c r="AI108" s="109"/>
     </row>
-    <row r="109" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A109" s="114"/>
       <c r="B109" s="114"/>
       <c r="C109" s="109"/>
       <c r="D109" s="109"/>
-      <c r="E109" s="109" t="e">
-        <v>#N/A</v>
+      <c r="E109" s="109" t="e" vm="1">
+        <v>#VALUE!</v>
       </c>
       <c r="F109" s="109"/>
       <c r="G109" s="109"/>
@@ -19074,13 +19944,13 @@
       <c r="AH109" s="109"/>
       <c r="AI109" s="109"/>
     </row>
-    <row r="110" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A110" s="114"/>
       <c r="B110" s="114"/>
       <c r="C110" s="109"/>
       <c r="D110" s="109"/>
-      <c r="E110" s="109" t="e">
-        <v>#N/A</v>
+      <c r="E110" s="109" t="e" vm="1">
+        <v>#VALUE!</v>
       </c>
       <c r="F110" s="109"/>
       <c r="G110" s="109"/>
@@ -19113,13 +19983,13 @@
       <c r="AH110" s="109"/>
       <c r="AI110" s="109"/>
     </row>
-    <row r="111" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A111" s="114"/>
       <c r="B111" s="114"/>
       <c r="C111" s="109"/>
       <c r="D111" s="109"/>
-      <c r="E111" s="109" t="e">
-        <v>#N/A</v>
+      <c r="E111" s="109" t="e" vm="1">
+        <v>#VALUE!</v>
       </c>
       <c r="F111" s="109"/>
       <c r="G111" s="109"/>
@@ -19152,13 +20022,13 @@
       <c r="AH111" s="109"/>
       <c r="AI111" s="109"/>
     </row>
-    <row r="112" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A112" s="114"/>
       <c r="B112" s="114"/>
       <c r="C112" s="109"/>
       <c r="D112" s="109"/>
-      <c r="E112" s="109" t="e">
-        <v>#N/A</v>
+      <c r="E112" s="109" t="e" vm="1">
+        <v>#VALUE!</v>
       </c>
       <c r="F112" s="109"/>
       <c r="G112" s="109"/>
@@ -19191,11 +20061,11 @@
       <c r="AH112" s="109"/>
       <c r="AI112" s="109"/>
     </row>
-    <row r="113" spans="3:35" x14ac:dyDescent="0.3">
+    <row r="113" spans="3:35" x14ac:dyDescent="0.25">
       <c r="C113" s="109"/>
       <c r="D113" s="109"/>
-      <c r="E113" s="109" t="e">
-        <v>#N/A</v>
+      <c r="E113" s="109" t="e" vm="1">
+        <v>#VALUE!</v>
       </c>
       <c r="F113" s="109"/>
       <c r="G113" s="109"/>
@@ -19228,11 +20098,11 @@
       <c r="AH113" s="109"/>
       <c r="AI113" s="109"/>
     </row>
-    <row r="114" spans="3:35" x14ac:dyDescent="0.3">
+    <row r="114" spans="3:35" x14ac:dyDescent="0.25">
       <c r="C114" s="108"/>
       <c r="D114" s="108"/>
-      <c r="E114" s="108" t="e">
-        <v>#N/A</v>
+      <c r="E114" s="108" t="e" vm="1">
+        <v>#VALUE!</v>
       </c>
       <c r="F114" s="108"/>
       <c r="G114" s="109"/>
@@ -19265,11 +20135,11 @@
       <c r="AH114" s="109"/>
       <c r="AI114" s="109"/>
     </row>
-    <row r="115" spans="3:35" x14ac:dyDescent="0.3">
+    <row r="115" spans="3:35" x14ac:dyDescent="0.25">
       <c r="C115" s="108"/>
       <c r="D115" s="108"/>
-      <c r="E115" s="108" t="e">
-        <v>#N/A</v>
+      <c r="E115" s="108" t="e" vm="1">
+        <v>#VALUE!</v>
       </c>
       <c r="F115" s="108"/>
       <c r="G115" s="108"/>
@@ -19302,11 +20172,11 @@
       <c r="AH115" s="114"/>
       <c r="AI115" s="114"/>
     </row>
-    <row r="116" spans="3:35" x14ac:dyDescent="0.3">
+    <row r="116" spans="3:35" x14ac:dyDescent="0.25">
       <c r="C116" s="108"/>
       <c r="D116" s="108"/>
-      <c r="E116" s="108" t="e">
-        <v>#N/A</v>
+      <c r="E116" s="108" t="e" vm="1">
+        <v>#VALUE!</v>
       </c>
       <c r="F116" s="108"/>
       <c r="G116" s="108"/>
@@ -19339,7 +20209,7 @@
       <c r="AH116" s="114"/>
       <c r="AI116" s="114"/>
     </row>
-    <row r="117" spans="3:35" x14ac:dyDescent="0.3">
+    <row r="117" spans="3:35" x14ac:dyDescent="0.25">
       <c r="C117" s="108"/>
       <c r="D117" s="108"/>
       <c r="E117" s="108"/>
@@ -19402,7 +20272,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -19412,7 +20282,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -19422,37 +20292,37 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:A6"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.33203125" customWidth="1"/>
+    <col min="1" max="1" width="22.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="17" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="17" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="17" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="27.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="17" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="27.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="17" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="17" t="s">
         <v>477</v>
       </c>

--- a/Revalidacion Moose Scorpion Gecko/RA_Moose_Scorpion.xlsx
+++ b/Revalidacion Moose Scorpion Gecko/RA_Moose_Scorpion.xlsx
@@ -327,7 +327,7 @@
     <definedName name="Vibracion_herramientas_ctrl">Listas_Controles!$CM$2:$CM$3</definedName>
     <definedName name="Vibracion_herramientas_epp">Listas_EPP!$CJ$2:$CJ$2</definedName>
   </definedNames>
-  <calcPr calcId="191028" fullCalcOnLoad="1"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -6347,7 +6347,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:S33"/>
+  <dimension ref="A1:S35"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -6395,7 +6395,7 @@
     <row r="2" spans="1:19" s="20" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="145" t="inlineStr">
         <is>
-          <t xml:space="preserve">REVALIDACION: Estaciones Moose/Scorpion de atornillado e inspección manual (JA100924-03, JA100924-06, JA100924-07, MS-550-03, MS-550-04, MS-550-05, MS-550-06, MS-550-07)</t>
+          <t xml:space="preserve">REVALIDACION: Estaciones Moose/Scorpion de atornillado e inspeccion manual (JA100924-03, JA100924-06, JA100924-07, MS-550-03, MS-550-04, MS-550-05, MS-550-06, MS-550-07)</t>
         </is>
       </c>
       <c r="B2" s="127"/>
@@ -6655,7 +6655,7 @@
       </c>
       <c r="L8" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
+          <t xml:space="preserve">Traje de cuarto limpio, cofia, guantes de nitrilo, cubrebocas, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
         </is>
       </c>
       <c r="M8" s="58" t="inlineStr">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="C9" s="56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paso 2 de 4: asegura la pieza con el seguro/clip manual de la fixtura (Partes Fijas)</t>
+          <t xml:space="preserve">Paso 2 de 4: asegura la pieza con el seguro/clip manual de la fixtura</t>
         </is>
       </c>
       <c r="D9" s="56" t="inlineStr">
@@ -6738,7 +6738,7 @@
         </is>
       </c>
       <c r="J9" s="51">
-        <f t="shared" ref="J9:J27" si="3">H9*I9</f>
+        <f t="shared" ref="J9:J35" si="3">H9*I9</f>
         <v>0</v>
       </c>
       <c r="K9" s="107" t="inlineStr">
@@ -6748,7 +6748,7 @@
       </c>
       <c r="L9" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
+          <t xml:space="preserve">Traje de cuarto limpio, cofia, guantes de nitrilo, cubrebocas, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
         </is>
       </c>
       <c r="M9" s="58" t="inlineStr">
@@ -6774,11 +6774,11 @@
         </is>
       </c>
       <c r="P9" s="61">
-        <f t="shared" ref="P9:P27" si="4">IF(O9=5,(J9*1),IF(O9=4,(J9*0.85),IF(O9=3,(J9*0.15),IF(O9=2,(J9*0.05),IF(O9=1,(J9*-0.0000000000000001),(J9*1))))))</f>
+        <f t="shared" ref="P9:P35" si="4">IF(O9=5,(J9*1),IF(O9=4,(J9*0.85),IF(O9=3,(J9*0.15),IF(O9=2,(J9*0.05),IF(O9=1,(J9*-0.0000000000000001),(J9*1))))))</f>
         <v>0</v>
       </c>
       <c r="Q9" s="60">
-        <f t="shared" ref="Q9:Q27" si="5">IF(J9=0,0,(P9-J9)/J9)</f>
+        <f t="shared" ref="Q9:Q35" si="5">IF(J9=0,0,(P9-J9)/J9)</f>
         <v>0</v>
       </c>
       <c r="R9" s="57"/>
@@ -6841,7 +6841,7 @@
       </c>
       <c r="L10" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
+          <t xml:space="preserve">Traje de cuarto limpio, cofia, guantes de nitrilo, cubrebocas, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
         </is>
       </c>
       <c r="M10" s="58" t="inlineStr">
@@ -6920,7 +6920,7 @@
       </c>
       <c r="I11" s="57" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J11" s="51">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="L11" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
+          <t xml:space="preserve">Traje de cuarto limpio, cofia, guantes de nitrilo, cubrebocas, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
         </is>
       </c>
       <c r="M11" s="58" t="inlineStr">
@@ -6983,7 +6983,7 @@
       </c>
       <c r="C12" s="56" t="inlineStr">
         <is>
-          <t xml:space="preserve">El sensor/pin Poka Yoke de la fixtura verifica que la pieza esté correctamente orientada antes de permitir el ciclo; el operador puede tener contacto accidental con el mecanismo al cargar la pieza</t>
+          <t xml:space="preserve">El sensor/pin Poka Yoke de la fixtura verifica que la pieza esté correctamente orientada; contacto accidental al cargar</t>
         </is>
       </c>
       <c r="D12" s="56" t="inlineStr">
@@ -7027,7 +7027,7 @@
       </c>
       <c r="L12" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
+          <t xml:space="preserve">Traje de cuarto limpio, cofia, guantes de nitrilo, cubrebocas, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
         </is>
       </c>
       <c r="M12" s="58" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="C13" s="56" t="inlineStr">
         <is>
-          <t xml:space="preserve">El escáner fijo lee el código de la pieza/etiqueta antes o durante el ciclo; el operador puede golpearse con el escáner o golpear material al cargar/descargar</t>
+          <t xml:space="preserve">El escáner fijo lee el código de la pieza/etiqueta antes o durante el ciclo</t>
         </is>
       </c>
       <c r="D13" s="56" t="inlineStr">
@@ -7120,7 +7120,7 @@
       </c>
       <c r="L13" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
+          <t xml:space="preserve">Traje de cuarto limpio, cofia, guantes de nitrilo, cubrebocas, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
         </is>
       </c>
       <c r="M13" s="58" t="inlineStr">
@@ -7169,7 +7169,7 @@
       </c>
       <c r="C14" s="56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Las islas/bloques de conexión eléctrica de alimentación y de sensores quedan accesibles en el área de trabajo durante la operación normal</t>
+          <t xml:space="preserve">Las islas/bloques de conexión eléctrica quedan accesibles en el área de trabajo durante la operación normal</t>
         </is>
       </c>
       <c r="D14" s="56" t="inlineStr">
@@ -7213,7 +7213,7 @@
       </c>
       <c r="L14" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7. Adicional para intervención eléctrica: guantes dieléctricos (clase según voltaje) y calzado aislante.</t>
+          <t xml:space="preserve">Traje de cuarto limpio, cofia, guantes de nitrilo, cubrebocas, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7. Adicional para intervención eléctrica: guantes dieléctricos (clase según voltaje) y calzado aislante.</t>
         </is>
       </c>
       <c r="M14" s="58" t="inlineStr">
@@ -7262,7 +7262,7 @@
       </c>
       <c r="C15" s="56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Algunas fixturas usan pistones neumáticos para bloqueo de pieza; el operador puede tener contacto con el mecanismo durante la carga/descarga</t>
+          <t xml:space="preserve">Algunas fixturas usan pistones neumáticos para bloqueo de pieza; contacto con el mecanismo durante la carga/descarga</t>
         </is>
       </c>
       <c r="D15" s="56" t="inlineStr">
@@ -7306,7 +7306,7 @@
       </c>
       <c r="L15" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
+          <t xml:space="preserve">Traje de cuarto limpio, cofia, guantes de nitrilo, cubrebocas, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
         </is>
       </c>
       <c r="M15" s="58" t="inlineStr">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="L16" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
+          <t xml:space="preserve">Traje de cuarto limpio, cofia, guantes de nitrilo, cubrebocas, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
         </is>
       </c>
       <c r="M16" s="58" t="inlineStr">
@@ -7438,32 +7438,32 @@
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A17" s="55" t="inlineStr">
         <is>
-          <t xml:space="preserve">No rutinario</t>
+          <t xml:space="preserve">Rutinario</t>
         </is>
       </c>
       <c r="B17" s="55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arranque de la estación al inicio de turno</t>
+          <t xml:space="preserve">Exposición a ruido del atornillador eléctrico en uso</t>
         </is>
       </c>
       <c r="C17" s="56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paso 1 de 2: energiza el switch general de la estación</t>
+          <t xml:space="preserve">El atornillador eléctrico manual genera ruido durante el apriete de tornillos a lo largo del turno</t>
         </is>
       </c>
       <c r="D17" s="56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eléctrico</t>
+          <t xml:space="preserve">Mecanico</t>
         </is>
       </c>
       <c r="E17" s="49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conductores energizados</t>
+          <t xml:space="preserve">Ruido</t>
         </is>
       </c>
       <c r="F17" s="49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Electrocución</t>
+          <t xml:space="preserve">Hipoacusia</t>
         </is>
       </c>
       <c r="G17" s="56" t="inlineStr">
@@ -7473,12 +7473,12 @@
       </c>
       <c r="H17" s="57" t="inlineStr">
         <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I17" s="57" t="inlineStr">
+        <is>
           <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="I17" s="57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J17" s="51">
@@ -7487,12 +7487,12 @@
       </c>
       <c r="K17" s="107" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOTO</t>
+          <t xml:space="preserve">tapones auditivos</t>
         </is>
       </c>
       <c r="L17" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7. Adicional para intervención eléctrica: guantes dieléctricos (clase según voltaje) y calzado aislante.</t>
+          <t xml:space="preserve">Traje de cuarto limpio, cofia, guantes de nitrilo, cubrebocas, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7. Adicional: protección auditiva (tapones) por uso del atornillador eléctrico.</t>
         </is>
       </c>
       <c r="M17" s="58" t="inlineStr">
@@ -7514,7 +7514,7 @@
       </c>
       <c r="O17" s="49" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="P17" s="61">
@@ -7531,17 +7531,17 @@
     <row r="18" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A18" s="55" t="inlineStr">
         <is>
-          <t xml:space="preserve">No rutinario</t>
+          <t xml:space="preserve">Rutinario</t>
         </is>
       </c>
       <c r="B18" s="55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arranque de la estación al inicio de turno</t>
+          <t xml:space="preserve">Vibración de mano-brazo por uso del atornillador manual</t>
         </is>
       </c>
       <c r="C18" s="56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paso 2 de 2: verifica luces indicadoras/status y realiza un ciclo de prueba si la estación lo requiere, confirmando que el área esté despejada</t>
+          <t xml:space="preserve">El operador sostiene y opera el atornillador manual de forma repetitiva durante el turno</t>
         </is>
       </c>
       <c r="D18" s="56" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="E18" s="49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Partes móviles</t>
+          <t xml:space="preserve">Vibración</t>
         </is>
       </c>
       <c r="F18" s="49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atrapamiento</t>
+          <t xml:space="preserve">Entumecimiento</t>
         </is>
       </c>
       <c r="G18" s="56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Control</t>
+          <t xml:space="preserve">Influencia</t>
         </is>
       </c>
       <c r="H18" s="57" t="inlineStr">
@@ -7571,7 +7571,7 @@
       </c>
       <c r="I18" s="57" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J18" s="51">
@@ -7580,12 +7580,12 @@
       </c>
       <c r="K18" s="107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resguardos mecánicos</t>
+          <t xml:space="preserve">rotación de tareas</t>
         </is>
       </c>
       <c r="L18" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
+          <t xml:space="preserve">Traje de cuarto limpio, cofia, guantes de nitrilo, cubrebocas, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
         </is>
       </c>
       <c r="M18" s="58" t="inlineStr">
@@ -7607,7 +7607,7 @@
       </c>
       <c r="O18" s="49" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="P18" s="61">
@@ -7624,32 +7624,32 @@
     <row r="19" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A19" s="55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Emergencia </t>
+          <t xml:space="preserve">No rutinario</t>
         </is>
       </c>
       <c r="B19" s="55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Activación del botón de paro de emergencia ante una condición insegura</t>
+          <t xml:space="preserve">Arranque de la estación al inicio de turno</t>
         </is>
       </c>
       <c r="C19" s="56" t="inlineStr">
         <is>
-          <t xml:space="preserve">El operador presiona el botón de paro de emergencia al detectar una condición insegura (atasco, ruido anormal, riesgo a persona) y notifica a su supervisor/mantenimiento</t>
+          <t xml:space="preserve">Paso 1 de 2: energiza el switch general de la estación</t>
         </is>
       </c>
       <c r="D19" s="56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mecanico</t>
+          <t xml:space="preserve">Eléctrico</t>
         </is>
       </c>
       <c r="E19" s="49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Partes móviles</t>
+          <t xml:space="preserve">Conductores energizados</t>
         </is>
       </c>
       <c r="F19" s="49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atrapamiento</t>
+          <t xml:space="preserve">Electrocución</t>
         </is>
       </c>
       <c r="G19" s="56" t="inlineStr">
@@ -7659,7 +7659,7 @@
       </c>
       <c r="H19" s="57" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="I19" s="57" t="inlineStr">
@@ -7673,15 +7673,108 @@
       </c>
       <c r="K19" s="107" t="inlineStr">
         <is>
-          <t xml:space="preserve">sensores</t>
+          <t xml:space="preserve">LOTO</t>
         </is>
       </c>
       <c r="L19" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
+          <t xml:space="preserve">Traje de cuarto limpio, cofia, guantes de nitrilo, cubrebocas, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7. Adicional para intervención eléctrica: guantes dieléctricos (clase según voltaje) y calzado aislante.</t>
         </is>
       </c>
       <c r="M19" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Procedimiento LOTO general de la estación: 16-HS20-8000-00017. 16-AT40-3318-00008
+16-AT40-3318-00009
+16-AT40-3318-00010
+16-AT40-3318-00011
+16-AT40-3318-00021
+16-AT40-3318-00024
+16-AT40-3318-00025
+(Front Assy Moose: numero de AV pendiente de confirmar, ilegible en la imagen enviada)</t>
+        </is>
+      </c>
+      <c r="N19" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O19" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="P19" s="61">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q19" s="60">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R19" s="57"/>
+      <c r="S19" s="57"/>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A20" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No rutinario</t>
+        </is>
+      </c>
+      <c r="B20" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Arranque de la estación al inicio de turno</t>
+        </is>
+      </c>
+      <c r="C20" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paso 2 de 2: verifica luces indicadoras/status y realiza un ciclo de prueba si la estación lo requiere, confirmando que el área esté despejada</t>
+        </is>
+      </c>
+      <c r="D20" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mecanico</t>
+        </is>
+      </c>
+      <c r="E20" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partes móviles</t>
+        </is>
+      </c>
+      <c r="F20" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Atrapamiento</t>
+        </is>
+      </c>
+      <c r="G20" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control</t>
+        </is>
+      </c>
+      <c r="H20" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I20" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J20" s="51">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K20" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resguardos mecánicos</t>
+        </is>
+      </c>
+      <c r="L20" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traje de cuarto limpio, cofia, guantes de nitrilo, cubrebocas, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
+        </is>
+      </c>
+      <c r="M20" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">16-AT40-3318-00008
 16-AT40-3318-00009
@@ -7693,88 +7786,88 @@
 (Front Assy Moose: numero de AV pendiente de confirmar, ilegible en la imagen enviada)</t>
         </is>
       </c>
-      <c r="N19" s="57" t="inlineStr">
+      <c r="N20" s="57" t="inlineStr">
         <is>
           <t xml:space="preserve">EHS / Automation</t>
         </is>
       </c>
-      <c r="O19" s="49" t="inlineStr">
+      <c r="O20" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="P19" s="61">
+      <c r="P20" s="61">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="Q19" s="60">
+      <c r="Q20" s="60">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="R19" s="57"/>
-      <c r="S19" s="57"/>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A20" s="55" t="inlineStr">
+      <c r="R20" s="57"/>
+      <c r="S20" s="57"/>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A21" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">Emergencia </t>
         </is>
       </c>
-      <c r="B20" s="55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Reinicio del equipo después de un paro de emergencia</t>
-        </is>
-      </c>
-      <c r="C20" s="56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Personal autorizado identifica y corrige la causa del paro, verifica que el área esté despejada antes de liberar el botón de paro y reiniciar el ciclo</t>
-        </is>
-      </c>
-      <c r="D20" s="56" t="inlineStr">
+      <c r="B21" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Activación del botón de paro de emergencia ante una condición insegura</t>
+        </is>
+      </c>
+      <c r="C21" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El operador presiona el botón de paro de emergencia al detectar una condición insegura y notifica a su supervisor/mantenimiento</t>
+        </is>
+      </c>
+      <c r="D21" s="56" t="inlineStr">
         <is>
           <t xml:space="preserve">Mecanico</t>
         </is>
       </c>
-      <c r="E20" s="49" t="inlineStr">
+      <c r="E21" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">Partes móviles</t>
         </is>
       </c>
-      <c r="F20" s="49" t="inlineStr">
+      <c r="F21" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">Atrapamiento</t>
         </is>
       </c>
-      <c r="G20" s="56" t="inlineStr">
+      <c r="G21" s="56" t="inlineStr">
         <is>
           <t xml:space="preserve">Control</t>
         </is>
       </c>
-      <c r="H20" s="57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="I20" s="57" t="inlineStr">
+      <c r="H21" s="57" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="J20" s="51">
+      <c r="I21" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J21" s="51">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K20" s="107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LOTO</t>
-        </is>
-      </c>
-      <c r="L20" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
-        </is>
-      </c>
-      <c r="M20" s="58" t="inlineStr">
+      <c r="K21" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sensores</t>
+        </is>
+      </c>
+      <c r="L21" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traje de cuarto limpio, cofia, guantes de nitrilo, cubrebocas, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
+        </is>
+      </c>
+      <c r="M21" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">16-AT40-3318-00008
 16-AT40-3318-00009
@@ -7786,88 +7879,1204 @@
 (Front Assy Moose: numero de AV pendiente de confirmar, ilegible en la imagen enviada)</t>
         </is>
       </c>
-      <c r="N20" s="57" t="inlineStr">
+      <c r="N21" s="57" t="inlineStr">
         <is>
           <t xml:space="preserve">EHS / Automation</t>
         </is>
       </c>
-      <c r="O20" s="49" t="inlineStr">
+      <c r="O21" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="P20" s="61">
+      <c r="P21" s="61">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="Q20" s="60">
+      <c r="Q21" s="60">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="R20" s="57"/>
-      <c r="S20" s="57"/>
-    </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A21" s="55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No rutinario</t>
-        </is>
-      </c>
-      <c r="B21" s="55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mantenimiento correctivo eléctrico</t>
-        </is>
-      </c>
-      <c r="C21" s="56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Paso 1 de 4: bloquea y etiqueta (LOTO) el switch general de desconexión antes de intervenir</t>
-        </is>
-      </c>
-      <c r="D21" s="56" t="inlineStr">
+      <c r="R21" s="57"/>
+      <c r="S21" s="57"/>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A22" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Emergencia </t>
+        </is>
+      </c>
+      <c r="B22" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reinicio del equipo después de un paro de emergencia</t>
+        </is>
+      </c>
+      <c r="C22" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Personal autorizado identifica y corrige la causa del paro, verifica el área despejada antes de liberar el botón y reiniciar el ciclo</t>
+        </is>
+      </c>
+      <c r="D22" s="56" t="inlineStr">
         <is>
           <t xml:space="preserve">Mecanico</t>
         </is>
       </c>
-      <c r="E21" s="49" t="inlineStr">
+      <c r="E22" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">Partes móviles</t>
         </is>
       </c>
-      <c r="F21" s="49" t="inlineStr">
+      <c r="F22" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">Atrapamiento</t>
         </is>
       </c>
-      <c r="G21" s="56" t="inlineStr">
+      <c r="G22" s="56" t="inlineStr">
         <is>
           <t xml:space="preserve">Control</t>
         </is>
       </c>
-      <c r="H21" s="57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="I21" s="57" t="inlineStr">
+      <c r="H22" s="57" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="J21" s="51">
+      <c r="I22" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J22" s="51">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K21" s="107" t="inlineStr">
+      <c r="K22" s="107" t="inlineStr">
         <is>
           <t xml:space="preserve">LOTO</t>
         </is>
       </c>
-      <c r="L21" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7. Adicional para intervención eléctrica: guantes dieléctricos (clase según voltaje) y calzado aislante.</t>
-        </is>
-      </c>
-      <c r="M21" s="58" t="inlineStr">
+      <c r="L22" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traje de cuarto limpio, cofia, guantes de nitrilo, cubrebocas, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7. Adicional para intervención eléctrica: guantes dieléctricos (clase según voltaje) y calzado aislante.</t>
+        </is>
+      </c>
+      <c r="M22" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Procedimiento LOTO general de la estación: 16-HS20-8000-00017. 16-AT40-3318-00008
+16-AT40-3318-00009
+16-AT40-3318-00010
+16-AT40-3318-00011
+16-AT40-3318-00021
+16-AT40-3318-00024
+16-AT40-3318-00025
+(Front Assy Moose: numero de AV pendiente de confirmar, ilegible en la imagen enviada)</t>
+        </is>
+      </c>
+      <c r="N22" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O22" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="P22" s="61">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q22" s="60">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R22" s="57"/>
+      <c r="S22" s="57"/>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A23" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No rutinario</t>
+        </is>
+      </c>
+      <c r="B23" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mantenimiento mecánico - Cambio de motor del atornillador eléctrico manual</t>
+        </is>
+      </c>
+      <c r="C23" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El personal de mantenimiento bloquea y etiqueta (LOTO) el switch general antes de cambio de motor del atornillador eléctrico manual</t>
+        </is>
+      </c>
+      <c r="D23" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mecanico</t>
+        </is>
+      </c>
+      <c r="E23" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partes móviles</t>
+        </is>
+      </c>
+      <c r="F23" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Atrapamiento</t>
+        </is>
+      </c>
+      <c r="G23" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control</t>
+        </is>
+      </c>
+      <c r="H23" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="I23" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="J23" s="51">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K23" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOTO</t>
+        </is>
+      </c>
+      <c r="L23" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traje de cuarto limpio, cofia, guantes de nitrilo, cubrebocas, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7. Adicional para intervención eléctrica: guantes dieléctricos (clase según voltaje) y calzado aislante.</t>
+        </is>
+      </c>
+      <c r="M23" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Procedimiento LOTO general de la estación: 16-HS20-8000-00017. 16-AT40-3318-00008
+16-AT40-3318-00009
+16-AT40-3318-00010
+16-AT40-3318-00011
+16-AT40-3318-00021
+16-AT40-3318-00024
+16-AT40-3318-00025
+(Front Assy Moose: numero de AV pendiente de confirmar, ilegible en la imagen enviada)</t>
+        </is>
+      </c>
+      <c r="N23" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O23" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="P23" s="61">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q23" s="60">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R23" s="57"/>
+      <c r="S23" s="57"/>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A24" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No rutinario</t>
+        </is>
+      </c>
+      <c r="B24" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mantenimiento mecánico - Cambio de broca/bit del atornillador</t>
+        </is>
+      </c>
+      <c r="C24" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El personal de mantenimiento bloquea y etiqueta (LOTO) el switch general antes de cambio de broca/bit del atornillador</t>
+        </is>
+      </c>
+      <c r="D24" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mecanico</t>
+        </is>
+      </c>
+      <c r="E24" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partes móviles</t>
+        </is>
+      </c>
+      <c r="F24" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Atrapamiento</t>
+        </is>
+      </c>
+      <c r="G24" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control</t>
+        </is>
+      </c>
+      <c r="H24" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="I24" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="J24" s="51">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K24" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOTO</t>
+        </is>
+      </c>
+      <c r="L24" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traje de cuarto limpio, cofia, guantes de nitrilo, cubrebocas, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7. Adicional para intervención eléctrica: guantes dieléctricos (clase según voltaje) y calzado aislante.</t>
+        </is>
+      </c>
+      <c r="M24" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Procedimiento LOTO general de la estación: 16-HS20-8000-00017. 16-AT40-3318-00008
+16-AT40-3318-00009
+16-AT40-3318-00010
+16-AT40-3318-00011
+16-AT40-3318-00021
+16-AT40-3318-00024
+16-AT40-3318-00025
+(Front Assy Moose: numero de AV pendiente de confirmar, ilegible en la imagen enviada)</t>
+        </is>
+      </c>
+      <c r="N24" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O24" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="P24" s="61">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q24" s="60">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R24" s="57"/>
+      <c r="S24" s="57"/>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A25" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No rutinario</t>
+        </is>
+      </c>
+      <c r="B25" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mantenimiento mecánico - Cambio/ajuste de la fixtura (topes, seguros)</t>
+        </is>
+      </c>
+      <c r="C25" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El personal de mantenimiento bloquea y etiqueta (LOTO) el switch general antes de cambio/ajuste de la fixtura (topes, seguros)</t>
+        </is>
+      </c>
+      <c r="D25" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mecanico</t>
+        </is>
+      </c>
+      <c r="E25" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partes móviles</t>
+        </is>
+      </c>
+      <c r="F25" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Atrapamiento</t>
+        </is>
+      </c>
+      <c r="G25" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control</t>
+        </is>
+      </c>
+      <c r="H25" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="I25" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J25" s="51">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K25" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOTO</t>
+        </is>
+      </c>
+      <c r="L25" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traje de cuarto limpio, cofia, guantes de nitrilo, cubrebocas, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7. Adicional para intervención eléctrica: guantes dieléctricos (clase según voltaje) y calzado aislante.</t>
+        </is>
+      </c>
+      <c r="M25" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Procedimiento LOTO general de la estación: 16-HS20-8000-00017. 16-AT40-3318-00008
+16-AT40-3318-00009
+16-AT40-3318-00010
+16-AT40-3318-00011
+16-AT40-3318-00021
+16-AT40-3318-00024
+16-AT40-3318-00025
+(Front Assy Moose: numero de AV pendiente de confirmar, ilegible en la imagen enviada)</t>
+        </is>
+      </c>
+      <c r="N25" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O25" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="P25" s="61">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q25" s="60">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R25" s="57"/>
+      <c r="S25" s="57"/>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A26" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No rutinario</t>
+        </is>
+      </c>
+      <c r="B26" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mantenimiento mecánico - Cambio de sensor Poka Yoke</t>
+        </is>
+      </c>
+      <c r="C26" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El personal de mantenimiento bloquea y etiqueta (LOTO) el switch general antes de cambio de sensor Poka Yoke</t>
+        </is>
+      </c>
+      <c r="D26" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mecanico</t>
+        </is>
+      </c>
+      <c r="E26" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partes móviles</t>
+        </is>
+      </c>
+      <c r="F26" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Atrapamiento</t>
+        </is>
+      </c>
+      <c r="G26" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control</t>
+        </is>
+      </c>
+      <c r="H26" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="I26" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J26" s="51">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K26" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOTO</t>
+        </is>
+      </c>
+      <c r="L26" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traje de cuarto limpio, cofia, guantes de nitrilo, cubrebocas, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7. Adicional para intervención eléctrica: guantes dieléctricos (clase según voltaje) y calzado aislante.</t>
+        </is>
+      </c>
+      <c r="M26" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Procedimiento LOTO general de la estación: 16-HS20-8000-00017. 16-AT40-3318-00008
+16-AT40-3318-00009
+16-AT40-3318-00010
+16-AT40-3318-00011
+16-AT40-3318-00021
+16-AT40-3318-00024
+16-AT40-3318-00025
+(Front Assy Moose: numero de AV pendiente de confirmar, ilegible en la imagen enviada)</t>
+        </is>
+      </c>
+      <c r="N26" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O26" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="P26" s="61">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q26" s="60">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R26" s="57"/>
+      <c r="S26" s="57"/>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A27" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No rutinario</t>
+        </is>
+      </c>
+      <c r="B27" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mantenimiento mecánico - Cambio/calibración del escáner de código</t>
+        </is>
+      </c>
+      <c r="C27" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El personal de mantenimiento bloquea y etiqueta (LOTO) el switch general antes de cambio/calibración del escáner de código</t>
+        </is>
+      </c>
+      <c r="D27" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mecanico</t>
+        </is>
+      </c>
+      <c r="E27" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partes móviles</t>
+        </is>
+      </c>
+      <c r="F27" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Atrapamiento</t>
+        </is>
+      </c>
+      <c r="G27" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control</t>
+        </is>
+      </c>
+      <c r="H27" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I27" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J27" s="51">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K27" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOTO</t>
+        </is>
+      </c>
+      <c r="L27" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traje de cuarto limpio, cofia, guantes de nitrilo, cubrebocas, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7. Adicional para intervención eléctrica: guantes dieléctricos (clase según voltaje) y calzado aislante.</t>
+        </is>
+      </c>
+      <c r="M27" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Procedimiento LOTO general de la estación: 16-HS20-8000-00017. 16-AT40-3318-00008
+16-AT40-3318-00009
+16-AT40-3318-00010
+16-AT40-3318-00011
+16-AT40-3318-00021
+16-AT40-3318-00024
+16-AT40-3318-00025
+(Front Assy Moose: numero de AV pendiente de confirmar, ilegible en la imagen enviada)</t>
+        </is>
+      </c>
+      <c r="N27" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O27" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="P27" s="61">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q27" s="60">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R27" s="57"/>
+      <c r="S27" s="57"/>
+    </row>
+    <row r="28" spans="1:19" s="19" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No rutinario</t>
+        </is>
+      </c>
+      <c r="B28" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mantenimiento mecánico - Cambio de cable/conector de alimentación del atornillador</t>
+        </is>
+      </c>
+      <c r="C28" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El personal de mantenimiento bloquea y etiqueta (LOTO) el switch general antes de cambio de cable/conector de alimentación del atornillador</t>
+        </is>
+      </c>
+      <c r="D28" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mecanico</t>
+        </is>
+      </c>
+      <c r="E28" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partes móviles</t>
+        </is>
+      </c>
+      <c r="F28" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Atrapamiento</t>
+        </is>
+      </c>
+      <c r="G28" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control</t>
+        </is>
+      </c>
+      <c r="H28" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="I28" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J28" s="51">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K28" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOTO</t>
+        </is>
+      </c>
+      <c r="L28" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traje de cuarto limpio, cofia, guantes de nitrilo, cubrebocas, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7. Adicional para intervención eléctrica: guantes dieléctricos (clase según voltaje) y calzado aislante.</t>
+        </is>
+      </c>
+      <c r="M28" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Procedimiento LOTO general de la estación: 16-HS20-8000-00017. 16-AT40-3318-00008
+16-AT40-3318-00009
+16-AT40-3318-00010
+16-AT40-3318-00011
+16-AT40-3318-00021
+16-AT40-3318-00024
+16-AT40-3318-00025
+(Front Assy Moose: numero de AV pendiente de confirmar, ilegible en la imagen enviada)</t>
+        </is>
+      </c>
+      <c r="N28" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O28" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="P28" s="61">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q28" s="60">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R28" s="57"/>
+      <c r="S28" s="57"/>
+    </row>
+    <row r="29" spans="1:19" s="19" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No rutinario</t>
+        </is>
+      </c>
+      <c r="B29" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mantenimiento neumático - cambio de manguera/cilindro de la fixtura</t>
+        </is>
+      </c>
+      <c r="C29" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El personal de mantenimiento despresuriza la línea y coloca el clip de bloqueo neumático tipo C portátil antes de intervenir cilindros o mangueras (estas fixturas no tienen válvula LOTO neumática integrada)</t>
+        </is>
+      </c>
+      <c r="D29" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mecanico</t>
+        </is>
+      </c>
+      <c r="E29" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sistema de presión</t>
+        </is>
+      </c>
+      <c r="F29" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Laceraciones</t>
+        </is>
+      </c>
+      <c r="G29" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control</t>
+        </is>
+      </c>
+      <c r="H29" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="I29" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J29" s="51">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K29" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Válvulas de alivio</t>
+        </is>
+      </c>
+      <c r="L29" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traje de cuarto limpio, cofia, guantes de nitrilo, cubrebocas, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7. Adicional: usar clip de bloqueo neumático tipo C (candado + tarjeta) en el acople rápido de aire en las estaciones sin válvula LOTO integrada.</t>
+        </is>
+      </c>
+      <c r="M29" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Procedimiento LOTO general de la estación: 16-HS20-8000-00017. 16-AT40-3318-00008
+16-AT40-3318-00009
+16-AT40-3318-00010
+16-AT40-3318-00011
+16-AT40-3318-00021
+16-AT40-3318-00024
+16-AT40-3318-00025
+(Front Assy Moose: numero de AV pendiente de confirmar, ilegible en la imagen enviada)</t>
+        </is>
+      </c>
+      <c r="N29" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O29" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="P29" s="61">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q29" s="60">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R29" s="57"/>
+      <c r="S29" s="57"/>
+    </row>
+    <row r="30" spans="1:19" s="19" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No rutinario</t>
+        </is>
+      </c>
+      <c r="B30" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mantenimiento neumático - limpieza/cambio de filtro regulador (FRL)</t>
+        </is>
+      </c>
+      <c r="C30" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El personal de mantenimiento despresuriza la línea antes de intervenir el filtro regulador de la estación</t>
+        </is>
+      </c>
+      <c r="D30" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mecanico</t>
+        </is>
+      </c>
+      <c r="E30" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sistema de presión</t>
+        </is>
+      </c>
+      <c r="F30" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Laceraciones</t>
+        </is>
+      </c>
+      <c r="G30" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control</t>
+        </is>
+      </c>
+      <c r="H30" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="I30" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J30" s="51">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K30" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Válvulas de alivio</t>
+        </is>
+      </c>
+      <c r="L30" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traje de cuarto limpio, cofia, guantes de nitrilo, cubrebocas, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7. Adicional: usar clip de bloqueo neumático tipo C (candado + tarjeta) en el acople rápido de aire en las estaciones sin válvula LOTO integrada.</t>
+        </is>
+      </c>
+      <c r="M30" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Procedimiento LOTO general de la estación: 16-HS20-8000-00017. 16-AT40-3318-00008
+16-AT40-3318-00009
+16-AT40-3318-00010
+16-AT40-3318-00011
+16-AT40-3318-00021
+16-AT40-3318-00024
+16-AT40-3318-00025
+(Front Assy Moose: numero de AV pendiente de confirmar, ilegible en la imagen enviada)</t>
+        </is>
+      </c>
+      <c r="N30" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O30" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="P30" s="61">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q30" s="60">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R30" s="57"/>
+      <c r="S30" s="57"/>
+    </row>
+    <row r="31" spans="1:19" s="19" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No rutinario</t>
+        </is>
+      </c>
+      <c r="B31" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mantenimiento correctivo eléctrico - Cambio de driver/tarjeta de control del atornillador</t>
+        </is>
+      </c>
+      <c r="C31" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El personal de mantenimiento bloquea y etiqueta (LOTO) el switch general, abre el gabinete eléctrico y realiza: cambio de driver/tarjeta de control del atornillador</t>
+        </is>
+      </c>
+      <c r="D31" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eléctrico</t>
+        </is>
+      </c>
+      <c r="E31" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Conductores energizados</t>
+        </is>
+      </c>
+      <c r="F31" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Electrocución</t>
+        </is>
+      </c>
+      <c r="G31" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control</t>
+        </is>
+      </c>
+      <c r="H31" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="I31" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J31" s="51">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K31" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOTO</t>
+        </is>
+      </c>
+      <c r="L31" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traje de cuarto limpio, cofia, guantes de nitrilo, cubrebocas, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7. Adicional para intervención eléctrica: guantes dieléctricos (clase según voltaje) y calzado aislante.</t>
+        </is>
+      </c>
+      <c r="M31" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Procedimiento LOTO general de la estación: 16-HS20-8000-00017. 16-AT40-3318-00008
+16-AT40-3318-00009
+16-AT40-3318-00010
+16-AT40-3318-00011
+16-AT40-3318-00021
+16-AT40-3318-00024
+16-AT40-3318-00025
+(Front Assy Moose: numero de AV pendiente de confirmar, ilegible en la imagen enviada)</t>
+        </is>
+      </c>
+      <c r="N31" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O31" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="P31" s="61">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q31" s="60">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R31" s="57"/>
+      <c r="S31" s="57"/>
+    </row>
+    <row r="32" spans="1:19" s="19" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No rutinario</t>
+        </is>
+      </c>
+      <c r="B32" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mantenimiento correctivo eléctrico - Revisión/cambio de cableado y conectores</t>
+        </is>
+      </c>
+      <c r="C32" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El personal de mantenimiento bloquea y etiqueta (LOTO) el switch general, abre el gabinete eléctrico y realiza: revisión/cambio de cableado y conectores</t>
+        </is>
+      </c>
+      <c r="D32" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eléctrico</t>
+        </is>
+      </c>
+      <c r="E32" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Conductores energizados</t>
+        </is>
+      </c>
+      <c r="F32" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Electrocución</t>
+        </is>
+      </c>
+      <c r="G32" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control</t>
+        </is>
+      </c>
+      <c r="H32" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="I32" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J32" s="51">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K32" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOTO</t>
+        </is>
+      </c>
+      <c r="L32" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traje de cuarto limpio, cofia, guantes de nitrilo, cubrebocas, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7. Adicional para intervención eléctrica: guantes dieléctricos (clase según voltaje) y calzado aislante.</t>
+        </is>
+      </c>
+      <c r="M32" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Procedimiento LOTO general de la estación: 16-HS20-8000-00017. 16-AT40-3318-00008
+16-AT40-3318-00009
+16-AT40-3318-00010
+16-AT40-3318-00011
+16-AT40-3318-00021
+16-AT40-3318-00024
+16-AT40-3318-00025
+(Front Assy Moose: numero de AV pendiente de confirmar, ilegible en la imagen enviada)</t>
+        </is>
+      </c>
+      <c r="N32" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O32" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="P32" s="61">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q32" s="60">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R32" s="57"/>
+      <c r="S32" s="57"/>
+    </row>
+    <row r="33" spans="1:19" s="19" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No rutinario</t>
+        </is>
+      </c>
+      <c r="B33" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mantenimiento correctivo eléctrico - diagnóstico general de gabinete</t>
+        </is>
+      </c>
+      <c r="C33" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El personal de mantenimiento abre el panel/gabinete eléctrico de la estación para diagnóstico de falla</t>
+        </is>
+      </c>
+      <c r="D33" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eléctrico</t>
+        </is>
+      </c>
+      <c r="E33" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Conductores energizados</t>
+        </is>
+      </c>
+      <c r="F33" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Electrocución</t>
+        </is>
+      </c>
+      <c r="G33" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control</t>
+        </is>
+      </c>
+      <c r="H33" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="I33" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="J33" s="51">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K33" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOTO</t>
+        </is>
+      </c>
+      <c r="L33" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traje de cuarto limpio, cofia, guantes de nitrilo, cubrebocas, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7. Adicional para intervención eléctrica: guantes dieléctricos (clase según voltaje) y calzado aislante.</t>
+        </is>
+      </c>
+      <c r="M33" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Procedimiento LOTO general de la estación: 16-HS20-8000-00017. 16-AT40-3318-00008
+16-AT40-3318-00009
+16-AT40-3318-00010
+16-AT40-3318-00011
+16-AT40-3318-00021
+16-AT40-3318-00024
+16-AT40-3318-00025
+(Front Assy Moose: numero de AV pendiente de confirmar, ilegible en la imagen enviada)</t>
+        </is>
+      </c>
+      <c r="N33" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O33" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="P33" s="61">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q33" s="60">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R33" s="57"/>
+      <c r="S33" s="57"/>
+    </row>
+    <row r="34" spans="1:19" s="19" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No rutinario</t>
+        </is>
+      </c>
+      <c r="B34" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Uso de herramientas manuales durante ajustes mecánicos</t>
+        </is>
+      </c>
+      <c r="C34" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El personal de mantenimiento usa llaves, desarmadores y otras herramientas manuales para los ajustes descritos arriba</t>
+        </is>
+      </c>
+      <c r="D34" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Herramientas</t>
+        </is>
+      </c>
+      <c r="E34" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Herramientas manuales</t>
+        </is>
+      </c>
+      <c r="F34" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Golpes</t>
+        </is>
+      </c>
+      <c r="G34" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control</t>
+        </is>
+      </c>
+      <c r="H34" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I34" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J34" s="51">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K34" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Capacitación</t>
+        </is>
+      </c>
+      <c r="L34" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traje de cuarto limpio, cofia, guantes de nitrilo, cubrebocas, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
+        </is>
+      </c>
+      <c r="M34" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">16-AT40-3318-00008
 16-AT40-3318-00009
@@ -7879,88 +9088,88 @@
 (Front Assy Moose: numero de AV pendiente de confirmar, ilegible en la imagen enviada)</t>
         </is>
       </c>
-      <c r="N21" s="57" t="inlineStr">
+      <c r="N34" s="57" t="inlineStr">
         <is>
           <t xml:space="preserve">EHS / Automation</t>
         </is>
       </c>
-      <c r="O21" s="49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="P21" s="61">
+      <c r="O34" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="P34" s="61">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="Q21" s="60">
+      <c r="Q34" s="60">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="R21" s="57"/>
-      <c r="S21" s="57"/>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A22" s="55" t="inlineStr">
+      <c r="R34" s="57"/>
+      <c r="S34" s="57"/>
+    </row>
+    <row r="35" spans="1:19" s="19" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">No rutinario</t>
         </is>
       </c>
-      <c r="B22" s="55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mantenimiento correctivo eléctrico</t>
-        </is>
-      </c>
-      <c r="C22" s="56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Paso 2 de 4: abre el panel/gabinete eléctrico de la estación para diagnóstico</t>
-        </is>
-      </c>
-      <c r="D22" s="56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Eléctrico</t>
-        </is>
-      </c>
-      <c r="E22" s="49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Conductores energizados</t>
-        </is>
-      </c>
-      <c r="F22" s="49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Electrocución</t>
-        </is>
-      </c>
-      <c r="G22" s="56" t="inlineStr">
+      <c r="B35" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Uso de aire comprimido para limpieza del equipo</t>
+        </is>
+      </c>
+      <c r="C35" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El personal de mantenimiento usa pistola de aire comprimido para limpiar polvo/residuos de la fixtura y el gabinete</t>
+        </is>
+      </c>
+      <c r="D35" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Herramientas</t>
+        </is>
+      </c>
+      <c r="E35" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partículas expulsadas</t>
+        </is>
+      </c>
+      <c r="F35" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lesión ocular</t>
+        </is>
+      </c>
+      <c r="G35" s="56" t="inlineStr">
         <is>
           <t xml:space="preserve">Control</t>
         </is>
       </c>
-      <c r="H22" s="57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5</t>
-        </is>
-      </c>
-      <c r="I22" s="57" t="inlineStr">
+      <c r="H35" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I35" s="57" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="J22" s="51">
+      <c r="J35" s="51">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K22" s="107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LOTO</t>
-        </is>
-      </c>
-      <c r="L22" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7. Adicional para intervención eléctrica: guantes dieléctricos (clase según voltaje) y calzado aislante.</t>
-        </is>
-      </c>
-      <c r="M22" s="58" t="inlineStr">
+      <c r="K35" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gafas</t>
+        </is>
+      </c>
+      <c r="L35" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traje de cuarto limpio, cofia, guantes de nitrilo, cubrebocas, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
+        </is>
+      </c>
+      <c r="M35" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">16-AT40-3318-00008
 16-AT40-3318-00009
@@ -7972,496 +9181,26 @@
 (Front Assy Moose: numero de AV pendiente de confirmar, ilegible en la imagen enviada)</t>
         </is>
       </c>
-      <c r="N22" s="57" t="inlineStr">
+      <c r="N35" s="57" t="inlineStr">
         <is>
           <t xml:space="preserve">EHS / Automation</t>
         </is>
       </c>
-      <c r="O22" s="49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="P22" s="61">
+      <c r="O35" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="P35" s="61">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="Q22" s="60">
+      <c r="Q35" s="60">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="R22" s="57"/>
-      <c r="S22" s="57"/>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A23" s="55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No rutinario</t>
-        </is>
-      </c>
-      <c r="B23" s="55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mantenimiento correctivo eléctrico</t>
-        </is>
-      </c>
-      <c r="C23" s="56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Paso 3 de 4: repara o reemplaza el componente dañado y cierra el gabinete</t>
-        </is>
-      </c>
-      <c r="D23" s="56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Eléctrico</t>
-        </is>
-      </c>
-      <c r="E23" s="49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Conductores energizados</t>
-        </is>
-      </c>
-      <c r="F23" s="49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Electrocución</t>
-        </is>
-      </c>
-      <c r="G23" s="56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Control</t>
-        </is>
-      </c>
-      <c r="H23" s="57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5</t>
-        </is>
-      </c>
-      <c r="I23" s="57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="J23" s="51">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K23" s="107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LOTO</t>
-        </is>
-      </c>
-      <c r="L23" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7. Adicional para intervención eléctrica: guantes dieléctricos (clase según voltaje) y calzado aislante.</t>
-        </is>
-      </c>
-      <c r="M23" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16-AT40-3318-00008
-16-AT40-3318-00009
-16-AT40-3318-00010
-16-AT40-3318-00011
-16-AT40-3318-00021
-16-AT40-3318-00024
-16-AT40-3318-00025
-(Front Assy Moose: numero de AV pendiente de confirmar, ilegible en la imagen enviada)</t>
-        </is>
-      </c>
-      <c r="N23" s="57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EHS / Automation</t>
-        </is>
-      </c>
-      <c r="O23" s="49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="P23" s="61">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Q23" s="60">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="R23" s="57"/>
-      <c r="S23" s="57"/>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A24" s="55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No rutinario</t>
-        </is>
-      </c>
-      <c r="B24" s="55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mantenimiento correctivo eléctrico</t>
-        </is>
-      </c>
-      <c r="C24" s="56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Paso 4 de 4: retira el candado/tarjeta de bloqueo (LOTO) y realiza una prueba funcional del equipo</t>
-        </is>
-      </c>
-      <c r="D24" s="56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mecanico</t>
-        </is>
-      </c>
-      <c r="E24" s="49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Partes móviles</t>
-        </is>
-      </c>
-      <c r="F24" s="49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Atrapamiento</t>
-        </is>
-      </c>
-      <c r="G24" s="56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Control</t>
-        </is>
-      </c>
-      <c r="H24" s="57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="I24" s="57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="J24" s="51">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K24" s="107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LOTO</t>
-        </is>
-      </c>
-      <c r="L24" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
-        </is>
-      </c>
-      <c r="M24" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16-AT40-3318-00008
-16-AT40-3318-00009
-16-AT40-3318-00010
-16-AT40-3318-00011
-16-AT40-3318-00021
-16-AT40-3318-00024
-16-AT40-3318-00025
-(Front Assy Moose: numero de AV pendiente de confirmar, ilegible en la imagen enviada)</t>
-        </is>
-      </c>
-      <c r="N24" s="57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EHS / Automation</t>
-        </is>
-      </c>
-      <c r="O24" s="49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="P24" s="61">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Q24" s="60">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="R24" s="57"/>
-      <c r="S24" s="57"/>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A25" s="55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No rutinario</t>
-        </is>
-      </c>
-      <c r="B25" s="55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mantenimiento neumático (en las estaciones con pistones de fixtura)</t>
-        </is>
-      </c>
-      <c r="C25" s="56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Paso 1 de 2: despresuriza la línea y coloca el clip de bloqueo neumático tipo C portátil (candado y tarjeta) en el acople rápido</t>
-        </is>
-      </c>
-      <c r="D25" s="56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mecanico</t>
-        </is>
-      </c>
-      <c r="E25" s="49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sistema de presión</t>
-        </is>
-      </c>
-      <c r="F25" s="49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Laceraciones</t>
-        </is>
-      </c>
-      <c r="G25" s="56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Control</t>
-        </is>
-      </c>
-      <c r="H25" s="57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="I25" s="57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="J25" s="51">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K25" s="107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Válvulas de alivio</t>
-        </is>
-      </c>
-      <c r="L25" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7. Adicional: usar clip de bloqueo neumático tipo C (candado + tarjeta) en el acople rápido de aire en las estaciones sin válvula LOTO integrada.</t>
-        </is>
-      </c>
-      <c r="M25" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16-AT40-3318-00008
-16-AT40-3318-00009
-16-AT40-3318-00010
-16-AT40-3318-00011
-16-AT40-3318-00021
-16-AT40-3318-00024
-16-AT40-3318-00025
-(Front Assy Moose: numero de AV pendiente de confirmar, ilegible en la imagen enviada)</t>
-        </is>
-      </c>
-      <c r="N25" s="57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EHS / Automation</t>
-        </is>
-      </c>
-      <c r="O25" s="49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="P25" s="61">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Q25" s="60">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="R25" s="57"/>
-      <c r="S25" s="57"/>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A26" s="55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No rutinario</t>
-        </is>
-      </c>
-      <c r="B26" s="55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mantenimiento neumático (en las estaciones con pistones de fixtura)</t>
-        </is>
-      </c>
-      <c r="C26" s="56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Paso 2 de 2: interviene cilindros o mangueras y verifica energía cero antes de retirar el bloqueo</t>
-        </is>
-      </c>
-      <c r="D26" s="56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mecanico</t>
-        </is>
-      </c>
-      <c r="E26" s="49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sistema de presión</t>
-        </is>
-      </c>
-      <c r="F26" s="49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Laceraciones</t>
-        </is>
-      </c>
-      <c r="G26" s="56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Control</t>
-        </is>
-      </c>
-      <c r="H26" s="57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="I26" s="57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="J26" s="51">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K26" s="107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Válvulas de alivio</t>
-        </is>
-      </c>
-      <c r="L26" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7. Adicional: usar clip de bloqueo neumático tipo C (candado + tarjeta) en el acople rápido de aire en las estaciones sin válvula LOTO integrada.</t>
-        </is>
-      </c>
-      <c r="M26" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16-AT40-3318-00008
-16-AT40-3318-00009
-16-AT40-3318-00010
-16-AT40-3318-00011
-16-AT40-3318-00021
-16-AT40-3318-00024
-16-AT40-3318-00025
-(Front Assy Moose: numero de AV pendiente de confirmar, ilegible en la imagen enviada)</t>
-        </is>
-      </c>
-      <c r="N26" s="57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EHS / Automation</t>
-        </is>
-      </c>
-      <c r="O26" s="49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="P26" s="61">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Q26" s="60">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="R26" s="57"/>
-      <c r="S26" s="57"/>
-    </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A27" s="55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No rutinario</t>
-        </is>
-      </c>
-      <c r="B27" s="55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mantenimiento al atornillador (bloqueo y etiquetado)</t>
-        </is>
-      </c>
-      <c r="C27" s="56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">El personal de mantenimiento bloquea el switch general de desconexión antes de intervenir el atornillador o la fixtura</t>
-        </is>
-      </c>
-      <c r="D27" s="56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mecanico</t>
-        </is>
-      </c>
-      <c r="E27" s="49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Partes móviles</t>
-        </is>
-      </c>
-      <c r="F27" s="49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Atrapamiento</t>
-        </is>
-      </c>
-      <c r="G27" s="56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Control</t>
-        </is>
-      </c>
-      <c r="H27" s="57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="I27" s="57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="J27" s="51">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K27" s="107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LOTO</t>
-        </is>
-      </c>
-      <c r="L27" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
-        </is>
-      </c>
-      <c r="M27" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16-AT40-3318-00008
-16-AT40-3318-00009
-16-AT40-3318-00010
-16-AT40-3318-00011
-16-AT40-3318-00021
-16-AT40-3318-00024
-16-AT40-3318-00025
-(Front Assy Moose: numero de AV pendiente de confirmar, ilegible en la imagen enviada)</t>
-        </is>
-      </c>
-      <c r="N27" s="57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EHS / Automation</t>
-        </is>
-      </c>
-      <c r="O27" s="49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4</t>
-        </is>
-      </c>
-      <c r="P27" s="61">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Q27" s="60">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="R27" s="57"/>
-      <c r="S27" s="57"/>
-    </row>
-    <row r="28" spans="1:19" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="K28" t="s">
-        <v>32</v>
-      </c>
+      <c r="R35" s="57"/>
+      <c r="S35" s="57"/>
     </row>
     <row r="29" spans="1:19" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="30" spans="1:19" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -8505,12 +9244,12 @@
     <mergeCell ref="N4:O4"/>
     <mergeCell ref="E3:G4"/>
   </mergeCells>
-  <conditionalFormatting sqref="J8:J27 P8:P27">
+  <conditionalFormatting sqref="J8:J35 P8:P35">
     <cfRule type="cellIs" dxfId="19" priority="2" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J8:J27">
+  <conditionalFormatting sqref="J8:J35">
     <cfRule type="cellIs" dxfId="18" priority="7" operator="between">
       <formula>17</formula>
       <formula>25</formula>
@@ -8528,7 +9267,7 @@
       <formula>3</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P8:P27">
+  <conditionalFormatting sqref="P8:P35">
     <cfRule type="cellIs" dxfId="14" priority="3" operator="between">
       <formula>17</formula>
       <formula>25</formula>
@@ -8553,7 +9292,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G28:G1048576" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>INDIRECT("Table4[Control-Influencia]")</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H8:I27" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H8:I35" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showDropDown="1" sqref="D28:D500" xr:uid="{00000000-0002-0000-0000-000003000000}">
